--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174669</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127174156</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127174628</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127174729</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127174143</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174669</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127174156</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127174628</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127174729</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127174143</v>
       </c>
       <c r="B6" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174669</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127174156</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127174628</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127174729</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127174143</v>
       </c>
       <c r="B6" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174669</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127174156</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127174628</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127174729</v>
       </c>
       <c r="B5" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127174143</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,9194 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128432850</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>435037</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6786731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128438000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>434956</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6786742</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128435467</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79621</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>435067</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6786325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128431234</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>434997</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6786800</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128435686</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>435051</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6786300</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128437673</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>434991</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6786554</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128430866</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>434953</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6786800</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128432871</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>435038</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6786734</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128435997</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>435005</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6786307</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128437284</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>434970</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6786443</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128437383</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>434967</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6786456</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128437182</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6786426</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128438143</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>435139</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6786742</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128431612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>434923</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6786779</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128451721</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>435244</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6786686</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128434385</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>435002</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6786518</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128436802</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>434960</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6786370</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128437687</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>434991</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6786553</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128437480</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>434949</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6786475</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128430705</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>434938</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6786813</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128435386</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>435059</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6786346</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128433812</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>435031</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6786549</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128430536</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>434931</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6786802</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128430028</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>434877</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6786784</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128447259</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>435291</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6786596</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128431051</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>434967</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6786800</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128431641</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>434924</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6786755</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128432204</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>434949</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6786757</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128432994</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>435043</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6786691</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128439013</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>435264</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6786618</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128434019</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>435020</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6786551</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128434393</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>435046</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6786471</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128437738</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>434991</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6786554</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128438813</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>435222</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6786653</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128433384</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79621</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>435063</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6786656</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128436784</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>434955</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6786364</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128429395</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>434860</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6786796</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128437639</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>434969</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6786551</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128431132</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6786804</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128431219</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>434992</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6786804</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128433187</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>435063</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6786656</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128437823</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6786577</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128431782</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>434911</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6786765</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128433488</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>435012</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6786629</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128437246</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>434984</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6786426</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128436819</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>434960</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6786373</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128438534</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>435172</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6786693</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128432659</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>434995</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6786753</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128432698</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>434995</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6786753</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128433166</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>435052</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6786677</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128432985</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>435046</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6786693</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128437455</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>434951</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6786479</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128434045</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>435021</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6786538</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128444055</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>435327</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6786584</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128432598</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>434985</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6786751</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128432333</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>434974</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6786786</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128433442</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>435015</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6786627</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128437830</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>434978</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6786579</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128437303</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>434966</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6786443</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128434528</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>435062</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6786456</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128430267</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>434893</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6786780</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128433951</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>435035</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6786547</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128430389</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>434924</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6786800</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128433768</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>435033</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6786548</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128437208</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>434976</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6786430</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128436694</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>434968</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6786352</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128439118</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>435271</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6786589</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128437095</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>434954</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6786401</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128437404</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>434956</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6786459</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128438202</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>435147</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6786737</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128433881</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>435035</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6786547</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128434479</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>435046</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6786473</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128435643</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>435049</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6786296</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128435513</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>435069</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6786320</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128438473</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>435172</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6786698</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128434156</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>435002</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6786518</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128452309</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>434956</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6786830</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128432486</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>434985</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6786751</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128437508</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>434949</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6786472</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128440167</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>435338</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6786560</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128439136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>435263</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6786587</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128430337</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>434911</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6786789</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128430113</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>434877</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6786784</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128433568</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>435001</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6786624</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Växer på levande tall på 1,5 meters höjd.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128430991</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>434968</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6786791</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,50 +1174,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128432850</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435037</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786731</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,45 +1393,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
-        <v>79621</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R12" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R13" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,38 +2049,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>57670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R15" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437284</v>
+        <v>128438143</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2172,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434970</v>
+        <v>435139</v>
       </c>
       <c r="R16" t="n">
-        <v>6786443</v>
+        <v>6786742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437383</v>
+        <v>128431612</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,39 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434967</v>
+        <v>434923</v>
       </c>
       <c r="R17" t="n">
-        <v>6786456</v>
+        <v>6786779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,45 +2375,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437182</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434976</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786426</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128438143</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435139</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786742</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128431612</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434923</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786779</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128436802</v>
+        <v>128437687</v>
       </c>
       <c r="B23" t="n">
         <v>78790</v>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434960</v>
+        <v>434991</v>
       </c>
       <c r="R23" t="n">
-        <v>6786370</v>
+        <v>6786553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437687</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78790</v>
+        <v>79650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434991</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786553</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437480</v>
+        <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>79650</v>
+        <v>78790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434949</v>
+        <v>434960</v>
       </c>
       <c r="R25" t="n">
-        <v>6786475</v>
+        <v>6786370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128430028</v>
+        <v>128431051</v>
       </c>
       <c r="B30" t="n">
         <v>79032</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434877</v>
+        <v>434967</v>
       </c>
       <c r="R30" t="n">
-        <v>6786784</v>
+        <v>6786800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128447259</v>
+        <v>128430028</v>
       </c>
       <c r="B31" t="n">
         <v>79032</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435291</v>
+        <v>434877</v>
       </c>
       <c r="R31" t="n">
-        <v>6786596</v>
+        <v>6786784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128431051</v>
+        <v>128447259</v>
       </c>
       <c r="B32" t="n">
         <v>79032</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434967</v>
+        <v>435291</v>
       </c>
       <c r="R32" t="n">
-        <v>6786800</v>
+        <v>6786596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128432994</v>
+        <v>128434019</v>
       </c>
       <c r="B35" t="n">
-        <v>78791</v>
+        <v>78790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435043</v>
+        <v>435020</v>
       </c>
       <c r="R35" t="n">
-        <v>6786691</v>
+        <v>6786551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128439013</v>
+        <v>128434393</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435264</v>
+        <v>435046</v>
       </c>
       <c r="R36" t="n">
-        <v>6786618</v>
+        <v>6786471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434019</v>
+        <v>128439013</v>
       </c>
       <c r="B37" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435020</v>
+        <v>435264</v>
       </c>
       <c r="R37" t="n">
-        <v>6786551</v>
+        <v>6786618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128434393</v>
+        <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435046</v>
+        <v>435043</v>
       </c>
       <c r="R38" t="n">
-        <v>6786471</v>
+        <v>6786691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4632,7 +4632,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128437738</v>
+        <v>128436784</v>
       </c>
       <c r="B39" t="n">
         <v>79650</v>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434991</v>
+        <v>434955</v>
       </c>
       <c r="R39" t="n">
-        <v>6786554</v>
+        <v>6786364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,7 +4739,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438813</v>
+        <v>128437738</v>
       </c>
       <c r="B40" t="n">
         <v>79650</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435222</v>
+        <v>434991</v>
       </c>
       <c r="R40" t="n">
-        <v>6786653</v>
+        <v>6786554</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128433384</v>
+        <v>128438813</v>
       </c>
       <c r="B41" t="n">
-        <v>79621</v>
+        <v>79650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435063</v>
+        <v>435222</v>
       </c>
       <c r="R41" t="n">
-        <v>6786656</v>
+        <v>6786653</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128436784</v>
+        <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79650</v>
+        <v>79621</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434955</v>
+        <v>435063</v>
       </c>
       <c r="R42" t="n">
-        <v>6786364</v>
+        <v>6786656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128429395</v>
+        <v>128431132</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>57670</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434860</v>
+        <v>434976</v>
       </c>
       <c r="R43" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5135,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5140,7 +5145,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437639</v>
+        <v>128431219</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,34 +5183,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434969</v>
+        <v>434992</v>
       </c>
       <c r="R44" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5237,7 +5247,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5247,7 +5257,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,10 +5284,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431132</v>
+        <v>128437639</v>
       </c>
       <c r="B45" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5285,39 +5295,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434976</v>
+        <v>434969</v>
       </c>
       <c r="R45" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5349,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5359,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5391,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128431219</v>
+        <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>57670</v>
+        <v>78791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5397,39 +5402,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434992</v>
+        <v>434860</v>
       </c>
       <c r="R46" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128431782</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,34 +5723,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434911</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786765</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128433488</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435012</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786629</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128437246</v>
+        <v>128433488</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5937,21 +5937,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434984</v>
+        <v>435012</v>
       </c>
       <c r="R51" t="n">
-        <v>6786426</v>
+        <v>6786629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128438534</v>
+        <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435172</v>
+        <v>434911</v>
       </c>
       <c r="R53" t="n">
-        <v>6786693</v>
+        <v>6786765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432659</v>
+        <v>128437455</v>
       </c>
       <c r="B54" t="n">
-        <v>79650</v>
+        <v>78791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R54" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,45 +6354,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432698</v>
+        <v>128444055</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>97355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434995</v>
+        <v>435327</v>
       </c>
       <c r="R55" t="n">
-        <v>6786753</v>
+        <v>6786584</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,7 +6461,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128433166</v>
+        <v>128434045</v>
       </c>
       <c r="B56" t="n">
         <v>79032</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435052</v>
+        <v>435021</v>
       </c>
       <c r="R56" t="n">
-        <v>6786677</v>
+        <v>6786538</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,12 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,7 +6568,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432985</v>
+        <v>128432659</v>
       </c>
       <c r="B57" t="n">
         <v>79650</v>
@@ -6604,14 +6599,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435046</v>
+        <v>434995</v>
       </c>
       <c r="R57" t="n">
-        <v>6786693</v>
+        <v>6786753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6653,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128437455</v>
+        <v>128432698</v>
       </c>
       <c r="B58" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,34 +6686,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434951</v>
+        <v>434995</v>
       </c>
       <c r="R58" t="n">
-        <v>6786479</v>
+        <v>6786753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6755,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,7 +6782,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128434045</v>
+        <v>128433166</v>
       </c>
       <c r="B59" t="n">
         <v>79032</v>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R59" t="n">
-        <v>6786538</v>
+        <v>6786677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6852,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6862,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128444055</v>
+        <v>128432985</v>
       </c>
       <c r="B60" t="n">
-        <v>97353</v>
+        <v>79650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435327</v>
+        <v>435046</v>
       </c>
       <c r="R60" t="n">
-        <v>6786584</v>
+        <v>6786693</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128432598</v>
+        <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434985</v>
+        <v>434893</v>
       </c>
       <c r="R61" t="n">
-        <v>6786751</v>
+        <v>6786780</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128432333</v>
+        <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>57670</v>
+        <v>79650</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434974</v>
+        <v>434966</v>
       </c>
       <c r="R62" t="n">
-        <v>6786786</v>
+        <v>6786443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7322,32 +7322,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437830</v>
+        <v>128434528</v>
       </c>
       <c r="B64" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434978</v>
+        <v>435062</v>
       </c>
       <c r="R64" t="n">
-        <v>6786579</v>
+        <v>6786456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437303</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
-        <v>79650</v>
+        <v>78791</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434966</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786443</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,32 +7536,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128434528</v>
+        <v>128437830</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435062</v>
+        <v>434978</v>
       </c>
       <c r="R66" t="n">
-        <v>6786456</v>
+        <v>6786579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128430267</v>
+        <v>128433951</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434893</v>
+        <v>435035</v>
       </c>
       <c r="R67" t="n">
-        <v>6786780</v>
+        <v>6786547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,7 +7750,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433951</v>
+        <v>128436694</v>
       </c>
       <c r="B68" t="n">
         <v>78791</v>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435035</v>
+        <v>434968</v>
       </c>
       <c r="R68" t="n">
-        <v>6786547</v>
+        <v>6786352</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128430389</v>
+        <v>128439118</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,34 +7868,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434924</v>
+        <v>435271</v>
       </c>
       <c r="R69" t="n">
-        <v>6786800</v>
+        <v>6786589</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7964,7 +7969,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128433768</v>
+        <v>128430389</v>
       </c>
       <c r="B70" t="n">
         <v>79032</v>
@@ -7995,14 +8000,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435033</v>
+        <v>434924</v>
       </c>
       <c r="R70" t="n">
-        <v>6786548</v>
+        <v>6786800</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8044,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128437208</v>
+        <v>128433768</v>
       </c>
       <c r="B71" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434976</v>
+        <v>435033</v>
       </c>
       <c r="R71" t="n">
-        <v>6786430</v>
+        <v>6786548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8151,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8178,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128436694</v>
+        <v>128437208</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>78790</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8189,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434968</v>
+        <v>434976</v>
       </c>
       <c r="R72" t="n">
-        <v>6786352</v>
+        <v>6786430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8248,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8258,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8285,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128439118</v>
+        <v>128433881</v>
       </c>
       <c r="B73" t="n">
-        <v>57670</v>
+        <v>78790</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8296,39 +8301,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435271</v>
+        <v>435035</v>
       </c>
       <c r="R73" t="n">
-        <v>6786589</v>
+        <v>6786547</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,7 +8397,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128437095</v>
+        <v>128434479</v>
       </c>
       <c r="B74" t="n">
         <v>79032</v>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434954</v>
+        <v>435046</v>
       </c>
       <c r="R74" t="n">
-        <v>6786401</v>
+        <v>6786473</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8477,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,7 +8509,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437404</v>
+        <v>128437095</v>
       </c>
       <c r="B75" t="n">
         <v>79032</v>
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434956</v>
+        <v>434954</v>
       </c>
       <c r="R75" t="n">
-        <v>6786459</v>
+        <v>6786401</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8579,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8611,7 +8616,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128438202</v>
+        <v>128437404</v>
       </c>
       <c r="B76" t="n">
         <v>79032</v>
@@ -8642,14 +8647,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435147</v>
+        <v>434956</v>
       </c>
       <c r="R76" t="n">
-        <v>6786737</v>
+        <v>6786459</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8681,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8691,12 +8696,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128433881</v>
+        <v>128438202</v>
       </c>
       <c r="B77" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8734,34 +8734,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435035</v>
+        <v>435147</v>
       </c>
       <c r="R77" t="n">
-        <v>6786547</v>
+        <v>6786737</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,7 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8830,7 +8835,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434479</v>
+        <v>128452309</v>
       </c>
       <c r="B78" t="n">
         <v>79032</v>
@@ -8861,14 +8866,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435046</v>
+        <v>434956</v>
       </c>
       <c r="R78" t="n">
-        <v>6786473</v>
+        <v>6786830</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8900,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8910,12 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435643</v>
+        <v>128438473</v>
       </c>
       <c r="B79" t="n">
-        <v>78791</v>
+        <v>57670</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,34 +8953,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435049</v>
+        <v>435172</v>
       </c>
       <c r="R79" t="n">
-        <v>6786296</v>
+        <v>6786698</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,7 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9049,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B80" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9060,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9084,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9119,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9129,7 +9134,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9156,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128438473</v>
+        <v>128435513</v>
       </c>
       <c r="B81" t="n">
-        <v>57670</v>
+        <v>78790</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9167,39 +9177,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435172</v>
+        <v>435069</v>
       </c>
       <c r="R81" t="n">
-        <v>6786698</v>
+        <v>6786320</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9268,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9279,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9303,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9338,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9348,12 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128452309</v>
+        <v>128440167</v>
       </c>
       <c r="B83" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434956</v>
+        <v>435338</v>
       </c>
       <c r="R83" t="n">
-        <v>6786830</v>
+        <v>6786560</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9455,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9465,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128432486</v>
+        <v>128430113</v>
       </c>
       <c r="B84" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9498,34 +9503,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434985</v>
+        <v>434877</v>
       </c>
       <c r="R84" t="n">
-        <v>6786751</v>
+        <v>6786784</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9567,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9577,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,10 +9604,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128437508</v>
+        <v>128439136</v>
       </c>
       <c r="B85" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,21 +9615,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9629,10 +9639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434949</v>
+        <v>435263</v>
       </c>
       <c r="R85" t="n">
-        <v>6786472</v>
+        <v>6786587</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9664,7 +9674,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9674,7 +9684,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9701,10 +9711,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128440167</v>
+        <v>128432486</v>
       </c>
       <c r="B86" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9712,39 +9722,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435338</v>
+        <v>434985</v>
       </c>
       <c r="R86" t="n">
-        <v>6786560</v>
+        <v>6786751</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9781,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9791,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,7 +9818,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128439136</v>
+        <v>128430337</v>
       </c>
       <c r="B87" t="n">
         <v>79032</v>
@@ -9844,14 +9849,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435263</v>
+        <v>434911</v>
       </c>
       <c r="R87" t="n">
-        <v>6786587</v>
+        <v>6786789</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9888,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9898,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9920,10 +9925,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128430337</v>
+        <v>128437508</v>
       </c>
       <c r="B88" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9931,34 +9936,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434911</v>
+        <v>434949</v>
       </c>
       <c r="R88" t="n">
-        <v>6786789</v>
+        <v>6786472</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9990,7 +9995,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10000,7 +10005,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10027,10 +10032,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128430113</v>
+        <v>128430991</v>
       </c>
       <c r="B89" t="n">
-        <v>57670</v>
+        <v>91380</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10038,39 +10043,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434877</v>
+        <v>434968</v>
       </c>
       <c r="R89" t="n">
-        <v>6786784</v>
+        <v>6786791</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10136,229 +10136,6 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>128433568</v>
-      </c>
-      <c r="B90" t="n">
-        <v>91378</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>435001</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6786624</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Växer på levande tall på 1,5 meters höjd.</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>128430991</v>
-      </c>
-      <c r="B91" t="n">
-        <v>91378</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>434968</v>
-      </c>
-      <c r="R91" t="n">
-        <v>6786791</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -2049,38 +2049,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437383</v>
+        <v>128435997</v>
       </c>
       <c r="B15" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434967</v>
+        <v>435005</v>
       </c>
       <c r="R15" t="n">
-        <v>6786456</v>
+        <v>6786307</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128438143</v>
+        <v>128437284</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2172,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435139</v>
+        <v>434970</v>
       </c>
       <c r="R16" t="n">
-        <v>6786742</v>
+        <v>6786443</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128431612</v>
+        <v>128437182</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,34 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434923</v>
+        <v>434976</v>
       </c>
       <c r="R17" t="n">
-        <v>6786779</v>
+        <v>6786426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,38 +2375,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128438143</v>
       </c>
       <c r="B19" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>435139</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128431612</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>434923</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431051</v>
+        <v>128431641</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434967</v>
+        <v>434924</v>
       </c>
       <c r="R30" t="n">
-        <v>6786800</v>
+        <v>6786755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128430028</v>
+        <v>128431051</v>
       </c>
       <c r="B31" t="n">
         <v>79032</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434877</v>
+        <v>434967</v>
       </c>
       <c r="R31" t="n">
-        <v>6786784</v>
+        <v>6786800</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128447259</v>
+        <v>128430028</v>
       </c>
       <c r="B32" t="n">
         <v>79032</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435291</v>
+        <v>434877</v>
       </c>
       <c r="R32" t="n">
-        <v>6786596</v>
+        <v>6786784</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128431641</v>
+        <v>128447259</v>
       </c>
       <c r="B33" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,34 +4001,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434924</v>
+        <v>435291</v>
       </c>
       <c r="R33" t="n">
-        <v>6786755</v>
+        <v>6786596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128431132</v>
+        <v>128429395</v>
       </c>
       <c r="B43" t="n">
-        <v>57670</v>
+        <v>78791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434976</v>
+        <v>434860</v>
       </c>
       <c r="R43" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,7 +5130,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5145,7 +5140,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B44" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5183,39 +5178,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R44" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5247,7 +5237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5257,7 +5247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5284,10 +5274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128437639</v>
+        <v>128431132</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5295,34 +5285,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434969</v>
+        <v>434976</v>
       </c>
       <c r="R45" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,7 +5349,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5359,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5391,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128429395</v>
+        <v>128431219</v>
       </c>
       <c r="B46" t="n">
-        <v>78791</v>
+        <v>57670</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5402,34 +5397,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434860</v>
+        <v>434992</v>
       </c>
       <c r="R46" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7001,45 +7001,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128430267</v>
+        <v>128434528</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434893</v>
+        <v>435062</v>
       </c>
       <c r="R61" t="n">
-        <v>6786780</v>
+        <v>6786456</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437303</v>
+        <v>128432598</v>
       </c>
       <c r="B62" t="n">
-        <v>79650</v>
+        <v>78791</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434966</v>
+        <v>434985</v>
       </c>
       <c r="R62" t="n">
-        <v>6786443</v>
+        <v>6786751</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128433442</v>
+        <v>128437830</v>
       </c>
       <c r="B63" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435015</v>
+        <v>434978</v>
       </c>
       <c r="R63" t="n">
-        <v>6786627</v>
+        <v>6786579</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,45 +7322,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128434528</v>
+        <v>128430267</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435062</v>
+        <v>434893</v>
       </c>
       <c r="R64" t="n">
-        <v>6786456</v>
+        <v>6786780</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128432598</v>
+        <v>128437303</v>
       </c>
       <c r="B65" t="n">
-        <v>78791</v>
+        <v>79650</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434985</v>
+        <v>434966</v>
       </c>
       <c r="R65" t="n">
-        <v>6786751</v>
+        <v>6786443</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,10 +7536,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128437830</v>
+        <v>128433442</v>
       </c>
       <c r="B66" t="n">
-        <v>78791</v>
+        <v>78790</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7547,21 +7547,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434978</v>
+        <v>435015</v>
       </c>
       <c r="R66" t="n">
-        <v>6786579</v>
+        <v>6786627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128433881</v>
+        <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8301,21 +8301,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435035</v>
+        <v>434954</v>
       </c>
       <c r="R73" t="n">
-        <v>6786547</v>
+        <v>6786401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128434479</v>
+        <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435046</v>
+        <v>435035</v>
       </c>
       <c r="R74" t="n">
-        <v>6786473</v>
+        <v>6786547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,12 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8509,7 +8504,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437095</v>
+        <v>128437404</v>
       </c>
       <c r="B75" t="n">
         <v>79032</v>
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434954</v>
+        <v>434956</v>
       </c>
       <c r="R75" t="n">
-        <v>6786401</v>
+        <v>6786459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8574,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8589,7 +8584,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8616,7 +8611,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128437404</v>
+        <v>128438202</v>
       </c>
       <c r="B76" t="n">
         <v>79032</v>
@@ -8647,14 +8642,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434956</v>
+        <v>435147</v>
       </c>
       <c r="R76" t="n">
-        <v>6786459</v>
+        <v>6786737</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8686,7 +8681,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8696,7 +8691,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,7 +8723,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128438202</v>
+        <v>128434479</v>
       </c>
       <c r="B77" t="n">
         <v>79032</v>
@@ -8754,14 +8754,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435147</v>
+        <v>435046</v>
       </c>
       <c r="R77" t="n">
-        <v>6786737</v>
+        <v>6786473</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128452309</v>
+        <v>128438473</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,34 +8846,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434956</v>
+        <v>435172</v>
       </c>
       <c r="R78" t="n">
-        <v>6786830</v>
+        <v>6786698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8920,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,39 +8958,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9027,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9059,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,21 +9070,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,12 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435513</v>
+        <v>128435643</v>
       </c>
       <c r="B81" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435069</v>
+        <v>435049</v>
       </c>
       <c r="R81" t="n">
-        <v>6786320</v>
+        <v>6786296</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128452309</v>
       </c>
       <c r="B82" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>434956</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,7 +1177,7 @@
         <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128435467</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>435067</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1351,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1361,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1424,7 +1419,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1463,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1473,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,45 +1500,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B10" t="n">
-        <v>79621</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1615,7 @@
         <v>128435686</v>
       </c>
       <c r="B11" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,50 +2049,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128435997</v>
+        <v>128431612</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435005</v>
+        <v>434923</v>
       </c>
       <c r="R15" t="n">
-        <v>6786307</v>
+        <v>6786779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437284</v>
+        <v>128437383</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2167,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434970</v>
+        <v>434967</v>
       </c>
       <c r="R16" t="n">
-        <v>6786443</v>
+        <v>6786456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437182</v>
+        <v>128438143</v>
       </c>
       <c r="B17" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,34 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434976</v>
+        <v>435139</v>
       </c>
       <c r="R17" t="n">
-        <v>6786426</v>
+        <v>6786742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,38 +2375,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437383</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434967</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786456</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128438143</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435139</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786742</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128431612</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434923</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786779</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>128433812</v>
       </c>
       <c r="B28" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>128430536</v>
       </c>
       <c r="B29" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431641</v>
+        <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434924</v>
+        <v>434967</v>
       </c>
       <c r="R30" t="n">
-        <v>6786755</v>
+        <v>6786800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R31" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R32" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128447259</v>
+        <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,34 +4001,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435291</v>
+        <v>434924</v>
       </c>
       <c r="R33" t="n">
-        <v>6786596</v>
+        <v>6786755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432204</v>
+        <v>128434393</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>78840</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434949</v>
+        <v>435046</v>
       </c>
       <c r="R34" t="n">
-        <v>6786757</v>
+        <v>6786471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434019</v>
+        <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>78790</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435020</v>
+        <v>434949</v>
       </c>
       <c r="R35" t="n">
-        <v>6786551</v>
+        <v>6786757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B36" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R36" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4421,7 +4421,7 @@
         <v>128439013</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436784</v>
+        <v>128438813</v>
       </c>
       <c r="B39" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434955</v>
+        <v>435222</v>
       </c>
       <c r="R39" t="n">
-        <v>6786364</v>
+        <v>6786653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437738</v>
+        <v>128433384</v>
       </c>
       <c r="B40" t="n">
-        <v>79650</v>
+        <v>79673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4750,21 +4750,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434991</v>
+        <v>435063</v>
       </c>
       <c r="R40" t="n">
-        <v>6786554</v>
+        <v>6786656</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128438813</v>
+        <v>128436784</v>
       </c>
       <c r="B41" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435222</v>
+        <v>434955</v>
       </c>
       <c r="R41" t="n">
-        <v>6786653</v>
+        <v>6786364</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128433384</v>
+        <v>128437738</v>
       </c>
       <c r="B42" t="n">
-        <v>79621</v>
+        <v>79702</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435063</v>
+        <v>434991</v>
       </c>
       <c r="R42" t="n">
-        <v>6786656</v>
+        <v>6786554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128429395</v>
+        <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,34 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434860</v>
+        <v>434969</v>
       </c>
       <c r="R43" t="n">
-        <v>6786796</v>
+        <v>6786551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437639</v>
+        <v>128429395</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,34 +5178,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434969</v>
+        <v>434860</v>
       </c>
       <c r="R44" t="n">
-        <v>6786551</v>
+        <v>6786796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5277,7 +5277,7 @@
         <v>128431132</v>
       </c>
       <c r="B45" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128431219</v>
       </c>
       <c r="B46" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128433488</v>
+        <v>128436819</v>
       </c>
       <c r="B51" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435012</v>
+        <v>434960</v>
       </c>
       <c r="R51" t="n">
-        <v>6786629</v>
+        <v>6786373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128436819</v>
+        <v>128433488</v>
       </c>
       <c r="B52" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434960</v>
+        <v>435012</v>
       </c>
       <c r="R52" t="n">
-        <v>6786373</v>
+        <v>6786629</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,7 +6143,7 @@
         <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128437455</v>
+        <v>128432659</v>
       </c>
       <c r="B54" t="n">
-        <v>78791</v>
+        <v>79702</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434951</v>
+        <v>434995</v>
       </c>
       <c r="R54" t="n">
-        <v>6786479</v>
+        <v>6786753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,32 +6354,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128444055</v>
+        <v>128432985</v>
       </c>
       <c r="B55" t="n">
-        <v>97355</v>
+        <v>79702</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435327</v>
+        <v>435046</v>
       </c>
       <c r="R55" t="n">
-        <v>6786584</v>
+        <v>6786693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,32 +6461,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128434045</v>
+        <v>128444055</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>97448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435021</v>
+        <v>435327</v>
       </c>
       <c r="R56" t="n">
-        <v>6786538</v>
+        <v>6786584</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432659</v>
+        <v>128437455</v>
       </c>
       <c r="B57" t="n">
-        <v>79650</v>
+        <v>78841</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,34 +6579,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R57" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432698</v>
+        <v>128434045</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6706,14 +6706,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R58" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128433166</v>
+        <v>128432698</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,14 +6813,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R59" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6862,12 +6862,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,10 +6889,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128432985</v>
+        <v>128433166</v>
       </c>
       <c r="B60" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6900,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435046</v>
+        <v>435052</v>
       </c>
       <c r="R60" t="n">
-        <v>6786693</v>
+        <v>6786677</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6959,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6969,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,32 +7001,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128434528</v>
+        <v>128437303</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79702</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435062</v>
+        <v>434966</v>
       </c>
       <c r="R61" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128432598</v>
+        <v>128430267</v>
       </c>
       <c r="B62" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434985</v>
+        <v>434893</v>
       </c>
       <c r="R62" t="n">
-        <v>6786751</v>
+        <v>6786780</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128437830</v>
+        <v>128433442</v>
       </c>
       <c r="B63" t="n">
-        <v>78791</v>
+        <v>78840</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434978</v>
+        <v>435015</v>
       </c>
       <c r="R63" t="n">
-        <v>6786579</v>
+        <v>6786627</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128430267</v>
+        <v>128437830</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,34 +7333,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434893</v>
+        <v>434978</v>
       </c>
       <c r="R64" t="n">
-        <v>6786780</v>
+        <v>6786579</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437303</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
-        <v>79650</v>
+        <v>78841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434966</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786443</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,32 +7536,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128433442</v>
+        <v>128434528</v>
       </c>
       <c r="B66" t="n">
-        <v>78790</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435015</v>
+        <v>435062</v>
       </c>
       <c r="R66" t="n">
-        <v>6786627</v>
+        <v>6786456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128433951</v>
+        <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>78791</v>
+        <v>57682</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435035</v>
+        <v>435271</v>
       </c>
       <c r="R67" t="n">
-        <v>6786547</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7755,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128436694</v>
+        <v>128437208</v>
       </c>
       <c r="B68" t="n">
-        <v>78791</v>
+        <v>78840</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,21 +7766,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434968</v>
+        <v>434976</v>
       </c>
       <c r="R68" t="n">
-        <v>6786352</v>
+        <v>6786430</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7835,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128439118</v>
+        <v>128430389</v>
       </c>
       <c r="B69" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,39 +7873,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435271</v>
+        <v>434924</v>
       </c>
       <c r="R69" t="n">
-        <v>6786589</v>
+        <v>6786800</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128430389</v>
+        <v>128433768</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8000,14 +8000,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434924</v>
+        <v>435033</v>
       </c>
       <c r="R70" t="n">
-        <v>6786800</v>
+        <v>6786548</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433768</v>
+        <v>128436694</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435033</v>
+        <v>434968</v>
       </c>
       <c r="R71" t="n">
-        <v>6786548</v>
+        <v>6786352</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128437208</v>
+        <v>128433951</v>
       </c>
       <c r="B72" t="n">
-        <v>78790</v>
+        <v>78841</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434976</v>
+        <v>435035</v>
       </c>
       <c r="R72" t="n">
-        <v>6786430</v>
+        <v>6786547</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8293,7 +8293,7 @@
         <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>128437404</v>
       </c>
       <c r="B75" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128438202</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>128434479</v>
       </c>
       <c r="B77" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128438473</v>
+        <v>128452309</v>
       </c>
       <c r="B78" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,39 +8846,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435172</v>
+        <v>434956</v>
       </c>
       <c r="R78" t="n">
-        <v>6786698</v>
+        <v>6786830</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8910,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8920,7 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128438473</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,34 +8953,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>435172</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786698</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,12 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B80" t="n">
-        <v>78790</v>
+        <v>79083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9070,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9129,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9139,7 +9134,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B81" t="n">
-        <v>78791</v>
+        <v>78840</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R81" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128452309</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434956</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786830</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128440167</v>
+        <v>128430113</v>
       </c>
       <c r="B83" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,19 +9411,19 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435338</v>
+        <v>434877</v>
       </c>
       <c r="R83" t="n">
-        <v>6786560</v>
+        <v>6786784</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9503,39 +9503,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R84" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9567,7 +9562,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9577,7 +9572,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9604,10 +9599,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128439136</v>
+        <v>128430337</v>
       </c>
       <c r="B85" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9635,14 +9630,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435263</v>
+        <v>434911</v>
       </c>
       <c r="R85" t="n">
-        <v>6786587</v>
+        <v>6786789</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9674,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9684,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9711,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128432486</v>
+        <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>78840</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9722,34 +9717,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434985</v>
+        <v>434949</v>
       </c>
       <c r="R86" t="n">
-        <v>6786751</v>
+        <v>6786472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9781,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9791,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9818,10 +9813,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128430337</v>
+        <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9849,14 +9844,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434911</v>
+        <v>435263</v>
       </c>
       <c r="R87" t="n">
-        <v>6786789</v>
+        <v>6786587</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9888,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9898,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9925,10 +9920,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128437508</v>
+        <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>78790</v>
+        <v>91472</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,34 +9931,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434949</v>
+        <v>434968</v>
       </c>
       <c r="R88" t="n">
-        <v>6786472</v>
+        <v>6786791</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9995,7 +9990,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10005,7 +10000,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10032,10 +10027,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128430991</v>
+        <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10061,16 +10056,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434968</v>
+        <v>435001</v>
       </c>
       <c r="R89" t="n">
-        <v>6786791</v>
+        <v>6786624</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10102,7 +10100,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10112,7 +10110,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10121,6 +10119,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10136,6 +10135,348 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128432333</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>434974</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6786786</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128526361</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skalhustjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>435184</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6786754</v>
+      </c>
+      <c r="S91" t="n">
+        <v>20</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128440167</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>435338</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6786560</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1388,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128438000</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1419,7 +1419,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434956</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786742</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B10" t="n">
         <v>8450</v>
@@ -1531,7 +1531,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R10" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128431612</v>
+        <v>128437284</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,34 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434923</v>
+        <v>434970</v>
       </c>
       <c r="R15" t="n">
-        <v>6786779</v>
+        <v>6786443</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437383</v>
+        <v>128437182</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>78841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,39 +2167,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434967</v>
+        <v>434976</v>
       </c>
       <c r="R16" t="n">
-        <v>6786456</v>
+        <v>6786426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,45 +2263,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128438143</v>
+        <v>128435997</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435139</v>
+        <v>435005</v>
       </c>
       <c r="R17" t="n">
-        <v>6786742</v>
+        <v>6786307</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,38 +2375,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128438143</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>435139</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128431612</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>434923</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128437687</v>
+        <v>128433812</v>
       </c>
       <c r="B23" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434991</v>
+        <v>435031</v>
       </c>
       <c r="R23" t="n">
-        <v>6786553</v>
+        <v>6786549</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437480</v>
+        <v>128430536</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434949</v>
+        <v>434931</v>
       </c>
       <c r="R24" t="n">
-        <v>6786475</v>
+        <v>6786802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128436802</v>
+        <v>128437687</v>
       </c>
       <c r="B25" t="n">
         <v>78840</v>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434960</v>
+        <v>434991</v>
       </c>
       <c r="R25" t="n">
-        <v>6786370</v>
+        <v>6786553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128430705</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434938</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786813</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,50 +3343,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128435386</v>
+        <v>128436802</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>78840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435059</v>
+        <v>434960</v>
       </c>
       <c r="R27" t="n">
-        <v>6786346</v>
+        <v>6786370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128433812</v>
+        <v>128430705</v>
       </c>
       <c r="B28" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,34 +3461,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435031</v>
+        <v>434938</v>
       </c>
       <c r="R28" t="n">
-        <v>6786549</v>
+        <v>6786813</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,45 +3557,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128430536</v>
+        <v>128435386</v>
       </c>
       <c r="B29" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434931</v>
+        <v>435059</v>
       </c>
       <c r="R29" t="n">
-        <v>6786802</v>
+        <v>6786346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128434393</v>
+        <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435046</v>
+        <v>435043</v>
       </c>
       <c r="R34" t="n">
-        <v>6786471</v>
+        <v>6786691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128439013</v>
+        <v>128434393</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435264</v>
+        <v>435046</v>
       </c>
       <c r="R37" t="n">
-        <v>6786618</v>
+        <v>6786471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128432994</v>
+        <v>128439013</v>
       </c>
       <c r="B38" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435043</v>
+        <v>435264</v>
       </c>
       <c r="R38" t="n">
-        <v>6786691</v>
+        <v>6786618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128438813</v>
+        <v>128433384</v>
       </c>
       <c r="B39" t="n">
-        <v>79702</v>
+        <v>79673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435222</v>
+        <v>435063</v>
       </c>
       <c r="R39" t="n">
-        <v>6786653</v>
+        <v>6786656</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128433384</v>
+        <v>128436784</v>
       </c>
       <c r="B40" t="n">
-        <v>79673</v>
+        <v>79702</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4750,21 +4750,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435063</v>
+        <v>434955</v>
       </c>
       <c r="R40" t="n">
-        <v>6786656</v>
+        <v>6786364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128436784</v>
+        <v>128437738</v>
       </c>
       <c r="B41" t="n">
         <v>79702</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434955</v>
+        <v>434991</v>
       </c>
       <c r="R41" t="n">
-        <v>6786364</v>
+        <v>6786554</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,7 +4953,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128437738</v>
+        <v>128438813</v>
       </c>
       <c r="B42" t="n">
         <v>79702</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434991</v>
+        <v>435222</v>
       </c>
       <c r="R42" t="n">
-        <v>6786554</v>
+        <v>6786653</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5167,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128429395</v>
+        <v>128431132</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,34 +5178,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434860</v>
+        <v>434976</v>
       </c>
       <c r="R44" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5237,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5247,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431132</v>
+        <v>128431219</v>
       </c>
       <c r="B45" t="n">
         <v>57682</v>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434976</v>
+        <v>434992</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5349,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5359,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5391,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128431219</v>
+        <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>57682</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5397,39 +5402,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434992</v>
+        <v>434860</v>
       </c>
       <c r="R46" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128436819</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>434960</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128433488</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>435012</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786629</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128436819</v>
+        <v>128431782</v>
       </c>
       <c r="B51" t="n">
         <v>78841</v>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434960</v>
+        <v>434911</v>
       </c>
       <c r="R51" t="n">
-        <v>6786373</v>
+        <v>6786765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128433488</v>
+        <v>128437246</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435012</v>
+        <v>434984</v>
       </c>
       <c r="R52" t="n">
-        <v>6786629</v>
+        <v>6786426</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128431782</v>
+        <v>128438534</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434911</v>
+        <v>435172</v>
       </c>
       <c r="R53" t="n">
-        <v>6786765</v>
+        <v>6786693</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432659</v>
+        <v>128437455</v>
       </c>
       <c r="B54" t="n">
-        <v>79702</v>
+        <v>78841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R54" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432985</v>
+        <v>128434045</v>
       </c>
       <c r="B55" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435046</v>
+        <v>435021</v>
       </c>
       <c r="R55" t="n">
-        <v>6786693</v>
+        <v>6786538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,45 +6461,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128444055</v>
+        <v>128432659</v>
       </c>
       <c r="B56" t="n">
-        <v>97448</v>
+        <v>79702</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435327</v>
+        <v>434995</v>
       </c>
       <c r="R56" t="n">
-        <v>6786584</v>
+        <v>6786753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128437455</v>
+        <v>128432698</v>
       </c>
       <c r="B57" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,34 +6579,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434951</v>
+        <v>434995</v>
       </c>
       <c r="R57" t="n">
-        <v>6786479</v>
+        <v>6786753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,7 +6675,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128434045</v>
+        <v>128433166</v>
       </c>
       <c r="B58" t="n">
         <v>79083</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R58" t="n">
-        <v>6786538</v>
+        <v>6786677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,7 +6755,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6782,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128432698</v>
+        <v>128432985</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6793,34 +6798,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434995</v>
+        <v>435046</v>
       </c>
       <c r="R59" t="n">
-        <v>6786753</v>
+        <v>6786693</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6852,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6862,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6889,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128433166</v>
+        <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6924,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435052</v>
+        <v>435327</v>
       </c>
       <c r="R60" t="n">
-        <v>6786677</v>
+        <v>6786584</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6959,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6969,12 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128437303</v>
+        <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434966</v>
+        <v>434893</v>
       </c>
       <c r="R61" t="n">
-        <v>6786443</v>
+        <v>6786780</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128430267</v>
+        <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434893</v>
+        <v>434966</v>
       </c>
       <c r="R62" t="n">
-        <v>6786780</v>
+        <v>6786443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128439118</v>
+        <v>128430389</v>
       </c>
       <c r="B67" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,39 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435271</v>
+        <v>434924</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786800</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7718,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7728,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128437208</v>
+        <v>128433768</v>
       </c>
       <c r="B68" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,21 +7761,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7790,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434976</v>
+        <v>435033</v>
       </c>
       <c r="R68" t="n">
-        <v>6786430</v>
+        <v>6786548</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7835,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7862,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128430389</v>
+        <v>128437208</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,34 +7868,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434924</v>
+        <v>434976</v>
       </c>
       <c r="R69" t="n">
-        <v>6786800</v>
+        <v>6786430</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128433768</v>
+        <v>128436694</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,21 +7975,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8004,10 +7999,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435033</v>
+        <v>434968</v>
       </c>
       <c r="R70" t="n">
-        <v>6786548</v>
+        <v>6786352</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8044,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,7 +8071,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128436694</v>
+        <v>128433951</v>
       </c>
       <c r="B71" t="n">
         <v>78841</v>
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434968</v>
+        <v>435035</v>
       </c>
       <c r="R71" t="n">
-        <v>6786352</v>
+        <v>6786547</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8141,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8151,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8178,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128433951</v>
+        <v>128439118</v>
       </c>
       <c r="B72" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,34 +8189,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435035</v>
+        <v>435271</v>
       </c>
       <c r="R72" t="n">
-        <v>6786547</v>
+        <v>6786589</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B83" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,39 +9391,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R83" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9455,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9465,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,7 +9487,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128432486</v>
+        <v>128430337</v>
       </c>
       <c r="B84" t="n">
         <v>79083</v>
@@ -9527,10 +9522,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434985</v>
+        <v>434911</v>
       </c>
       <c r="R84" t="n">
-        <v>6786751</v>
+        <v>6786789</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9572,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,10 +9594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128430337</v>
+        <v>128437508</v>
       </c>
       <c r="B85" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9610,34 +9605,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434911</v>
+        <v>434949</v>
       </c>
       <c r="R85" t="n">
-        <v>6786789</v>
+        <v>6786472</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9664,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9674,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,10 +9701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128437508</v>
+        <v>128439136</v>
       </c>
       <c r="B86" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,21 +9712,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9741,10 +9736,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434949</v>
+        <v>435263</v>
       </c>
       <c r="R86" t="n">
-        <v>6786472</v>
+        <v>6786587</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9771,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9781,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,10 +9808,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128439136</v>
+        <v>128430113</v>
       </c>
       <c r="B87" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9824,34 +9819,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435263</v>
+        <v>434877</v>
       </c>
       <c r="R87" t="n">
-        <v>6786587</v>
+        <v>6786784</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,45 +1174,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128432850</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>435037</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1249,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,45 +1286,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128435467</v>
+        <v>128438000</v>
       </c>
       <c r="B8" t="n">
-        <v>79673</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435067</v>
+        <v>434956</v>
       </c>
       <c r="R8" t="n">
-        <v>6786325</v>
+        <v>6786742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1361,7 +1371,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,50 +1398,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128431234</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>434997</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1473,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,50 +1505,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128438000</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434956</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786742</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128433812</v>
+        <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435031</v>
+        <v>434991</v>
       </c>
       <c r="R23" t="n">
-        <v>6786549</v>
+        <v>6786553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128430536</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434931</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786802</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437687</v>
+        <v>128436802</v>
       </c>
       <c r="B25" t="n">
         <v>78840</v>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434991</v>
+        <v>434960</v>
       </c>
       <c r="R25" t="n">
-        <v>6786553</v>
+        <v>6786370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128436802</v>
+        <v>128433812</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434960</v>
+        <v>435031</v>
       </c>
       <c r="R27" t="n">
-        <v>6786370</v>
+        <v>6786549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430705</v>
+        <v>128430536</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434938</v>
+        <v>434931</v>
       </c>
       <c r="R28" t="n">
-        <v>6786813</v>
+        <v>6786802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5167,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431132</v>
+        <v>128429395</v>
       </c>
       <c r="B44" t="n">
-        <v>57682</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,39 +5178,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434976</v>
+        <v>434860</v>
       </c>
       <c r="R44" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,7 +5237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5274,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431219</v>
+        <v>128431132</v>
       </c>
       <c r="B45" t="n">
         <v>57682</v>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434992</v>
+        <v>434976</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5354,7 +5349,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5359,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5391,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128429395</v>
+        <v>128431219</v>
       </c>
       <c r="B46" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5402,34 +5397,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434860</v>
+        <v>434992</v>
       </c>
       <c r="R46" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128437455</v>
+        <v>128434045</v>
       </c>
       <c r="B54" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,21 +6258,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434951</v>
+        <v>435021</v>
       </c>
       <c r="R54" t="n">
-        <v>6786479</v>
+        <v>6786538</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128434045</v>
+        <v>128432659</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435021</v>
+        <v>434995</v>
       </c>
       <c r="R55" t="n">
-        <v>6786538</v>
+        <v>6786753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432659</v>
+        <v>128432698</v>
       </c>
       <c r="B56" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,7 +6568,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432698</v>
+        <v>128433166</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6599,14 +6599,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434995</v>
+        <v>435052</v>
       </c>
       <c r="R57" t="n">
-        <v>6786753</v>
+        <v>6786677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128433166</v>
+        <v>128432985</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6686,21 +6691,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6710,10 +6715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435052</v>
+        <v>435046</v>
       </c>
       <c r="R58" t="n">
-        <v>6786677</v>
+        <v>6786693</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,12 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128432985</v>
+        <v>128437455</v>
       </c>
       <c r="B59" t="n">
-        <v>79702</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435046</v>
+        <v>434951</v>
       </c>
       <c r="R59" t="n">
-        <v>6786693</v>
+        <v>6786479</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128430389</v>
+        <v>128436694</v>
       </c>
       <c r="B67" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434924</v>
+        <v>434968</v>
       </c>
       <c r="R67" t="n">
-        <v>6786800</v>
+        <v>6786352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433768</v>
+        <v>128433951</v>
       </c>
       <c r="B68" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,21 +7761,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435033</v>
+        <v>435035</v>
       </c>
       <c r="R68" t="n">
-        <v>6786548</v>
+        <v>6786547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128437208</v>
+        <v>128430389</v>
       </c>
       <c r="B69" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,34 +7868,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434976</v>
+        <v>434924</v>
       </c>
       <c r="R69" t="n">
-        <v>6786430</v>
+        <v>6786800</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128436694</v>
+        <v>128433768</v>
       </c>
       <c r="B70" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,21 +7975,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434968</v>
+        <v>435033</v>
       </c>
       <c r="R70" t="n">
-        <v>6786352</v>
+        <v>6786548</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433951</v>
+        <v>128437208</v>
       </c>
       <c r="B71" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,21 +8082,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8106,10 +8106,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435035</v>
+        <v>434976</v>
       </c>
       <c r="R71" t="n">
-        <v>6786547</v>
+        <v>6786430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B80" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R80" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,12 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B81" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,21 +9172,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9196,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R81" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B82" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128437687</v>
+        <v>128433812</v>
       </c>
       <c r="B23" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434991</v>
+        <v>435031</v>
       </c>
       <c r="R23" t="n">
-        <v>6786553</v>
+        <v>6786549</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437480</v>
+        <v>128430536</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434949</v>
+        <v>434931</v>
       </c>
       <c r="R24" t="n">
-        <v>6786475</v>
+        <v>6786802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128436802</v>
+        <v>128437687</v>
       </c>
       <c r="B25" t="n">
         <v>78840</v>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434960</v>
+        <v>434991</v>
       </c>
       <c r="R25" t="n">
-        <v>6786370</v>
+        <v>6786553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128430705</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434938</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786813</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128433812</v>
+        <v>128436802</v>
       </c>
       <c r="B27" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435031</v>
+        <v>434960</v>
       </c>
       <c r="R27" t="n">
-        <v>6786549</v>
+        <v>6786370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430536</v>
+        <v>128430705</v>
       </c>
       <c r="B28" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434931</v>
+        <v>434938</v>
       </c>
       <c r="R28" t="n">
-        <v>6786802</v>
+        <v>6786813</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432994</v>
+        <v>128432204</v>
       </c>
       <c r="B34" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435043</v>
+        <v>434949</v>
       </c>
       <c r="R34" t="n">
-        <v>6786691</v>
+        <v>6786757</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128432204</v>
+        <v>128434019</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434949</v>
+        <v>435020</v>
       </c>
       <c r="R35" t="n">
-        <v>6786757</v>
+        <v>6786551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,7 +4311,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434019</v>
+        <v>128434393</v>
       </c>
       <c r="B36" t="n">
         <v>78840</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435020</v>
+        <v>435046</v>
       </c>
       <c r="R36" t="n">
-        <v>6786551</v>
+        <v>6786471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434393</v>
+        <v>128439013</v>
       </c>
       <c r="B37" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435046</v>
+        <v>435264</v>
       </c>
       <c r="R37" t="n">
-        <v>6786471</v>
+        <v>6786618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128439013</v>
+        <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435264</v>
+        <v>435043</v>
       </c>
       <c r="R38" t="n">
-        <v>6786618</v>
+        <v>6786691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128436819</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434960</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786373</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128433488</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435012</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786629</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128431782</v>
+        <v>128436819</v>
       </c>
       <c r="B51" t="n">
         <v>78841</v>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434911</v>
+        <v>434960</v>
       </c>
       <c r="R51" t="n">
-        <v>6786765</v>
+        <v>6786373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128437246</v>
+        <v>128433488</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434984</v>
+        <v>435012</v>
       </c>
       <c r="R52" t="n">
-        <v>6786426</v>
+        <v>6786629</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128438534</v>
+        <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435172</v>
+        <v>434911</v>
       </c>
       <c r="R53" t="n">
-        <v>6786693</v>
+        <v>6786765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128436694</v>
+        <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434968</v>
+        <v>435271</v>
       </c>
       <c r="R67" t="n">
-        <v>6786352</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,7 +7755,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433951</v>
+        <v>128436694</v>
       </c>
       <c r="B68" t="n">
         <v>78841</v>
@@ -7785,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435035</v>
+        <v>434968</v>
       </c>
       <c r="R68" t="n">
-        <v>6786547</v>
+        <v>6786352</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7835,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128430389</v>
+        <v>128433951</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,34 +7873,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434924</v>
+        <v>435035</v>
       </c>
       <c r="R69" t="n">
-        <v>6786800</v>
+        <v>6786547</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7964,7 +7969,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128433768</v>
+        <v>128430389</v>
       </c>
       <c r="B70" t="n">
         <v>79083</v>
@@ -7995,14 +8000,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435033</v>
+        <v>434924</v>
       </c>
       <c r="R70" t="n">
-        <v>6786548</v>
+        <v>6786800</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8044,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128437208</v>
+        <v>128433768</v>
       </c>
       <c r="B71" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434976</v>
+        <v>435033</v>
       </c>
       <c r="R71" t="n">
-        <v>6786430</v>
+        <v>6786548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8151,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8178,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128439118</v>
+        <v>128437208</v>
       </c>
       <c r="B72" t="n">
-        <v>57682</v>
+        <v>78840</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8189,39 +8194,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435271</v>
+        <v>434976</v>
       </c>
       <c r="R72" t="n">
-        <v>6786589</v>
+        <v>6786430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>128432333</v>
       </c>
       <c r="B90" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>128526361</v>
       </c>
       <c r="B91" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>128440167</v>
       </c>
       <c r="B92" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,50 +1174,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128432850</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435037</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786731</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,45 +1393,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128431234</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434997</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786800</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,7 +1508,7 @@
         <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>128435686</v>
       </c>
       <c r="B11" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R12" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R13" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437284</v>
+        <v>128431612</v>
       </c>
       <c r="B15" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,34 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434970</v>
+        <v>434923</v>
       </c>
       <c r="R15" t="n">
-        <v>6786443</v>
+        <v>6786779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437182</v>
+        <v>128438143</v>
       </c>
       <c r="B16" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,34 +2167,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434976</v>
+        <v>435139</v>
       </c>
       <c r="R16" t="n">
-        <v>6786426</v>
+        <v>6786742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,38 +2263,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R17" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437383</v>
+        <v>128437284</v>
       </c>
       <c r="B18" t="n">
-        <v>57682</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,39 +2386,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434967</v>
+        <v>434970</v>
       </c>
       <c r="R18" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128438143</v>
+        <v>128437182</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2493,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435139</v>
+        <v>434976</v>
       </c>
       <c r="R19" t="n">
-        <v>6786742</v>
+        <v>6786426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2552,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2562,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,45 +2589,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128431612</v>
+        <v>128435997</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434923</v>
+        <v>435005</v>
       </c>
       <c r="R20" t="n">
-        <v>6786779</v>
+        <v>6786307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128433812</v>
+        <v>128430705</v>
       </c>
       <c r="B23" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,34 +2926,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435031</v>
+        <v>434938</v>
       </c>
       <c r="R23" t="n">
-        <v>6786549</v>
+        <v>6786813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,45 +3022,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128430536</v>
+        <v>128435386</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434931</v>
+        <v>435059</v>
       </c>
       <c r="R24" t="n">
-        <v>6786802</v>
+        <v>6786346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437687</v>
+        <v>128430536</v>
       </c>
       <c r="B25" t="n">
-        <v>78840</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434991</v>
+        <v>434931</v>
       </c>
       <c r="R25" t="n">
-        <v>6786553</v>
+        <v>6786802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128437687</v>
       </c>
       <c r="B26" t="n">
-        <v>79702</v>
+        <v>78844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3271,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434991</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128436802</v>
+        <v>128437480</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>79706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434960</v>
+        <v>434949</v>
       </c>
       <c r="R27" t="n">
-        <v>6786370</v>
+        <v>6786475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430705</v>
+        <v>128436802</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,34 +3466,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434938</v>
+        <v>434960</v>
       </c>
       <c r="R28" t="n">
-        <v>6786813</v>
+        <v>6786370</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,50 +3562,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128435386</v>
+        <v>128433812</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435059</v>
+        <v>435031</v>
       </c>
       <c r="R29" t="n">
-        <v>6786346</v>
+        <v>6786549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R30" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R31" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R32" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3993,7 +3993,7 @@
         <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432204</v>
+        <v>128439013</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4128,14 +4128,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434949</v>
+        <v>435264</v>
       </c>
       <c r="R34" t="n">
-        <v>6786757</v>
+        <v>6786618</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434019</v>
+        <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435020</v>
+        <v>434949</v>
       </c>
       <c r="R35" t="n">
-        <v>6786551</v>
+        <v>6786757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B36" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R36" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128439013</v>
+        <v>128434393</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435264</v>
+        <v>435046</v>
       </c>
       <c r="R37" t="n">
-        <v>6786618</v>
+        <v>6786471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4528,7 +4528,7 @@
         <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128433384</v>
+        <v>128436784</v>
       </c>
       <c r="B39" t="n">
-        <v>79673</v>
+        <v>79706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435063</v>
+        <v>434955</v>
       </c>
       <c r="R39" t="n">
-        <v>6786656</v>
+        <v>6786364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436784</v>
+        <v>128437738</v>
       </c>
       <c r="B40" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434955</v>
+        <v>434991</v>
       </c>
       <c r="R40" t="n">
-        <v>6786364</v>
+        <v>6786554</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437738</v>
+        <v>128438813</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434991</v>
+        <v>435222</v>
       </c>
       <c r="R41" t="n">
-        <v>6786554</v>
+        <v>6786653</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128438813</v>
+        <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79702</v>
+        <v>79677</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435222</v>
+        <v>435063</v>
       </c>
       <c r="R42" t="n">
-        <v>6786653</v>
+        <v>6786656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5063,7 +5063,7 @@
         <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128429395</v>
+        <v>128431132</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>57686</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,34 +5178,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434860</v>
+        <v>434976</v>
       </c>
       <c r="R44" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5237,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5247,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431132</v>
+        <v>128431219</v>
       </c>
       <c r="B45" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434976</v>
+        <v>434992</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5349,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5359,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5391,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128431219</v>
+        <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>57682</v>
+        <v>78845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5397,39 +5402,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434992</v>
+        <v>434860</v>
       </c>
       <c r="R46" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>128436819</v>
       </c>
       <c r="B51" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>128433488</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128434045</v>
+        <v>128433166</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R54" t="n">
-        <v>6786538</v>
+        <v>6786677</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432659</v>
+        <v>128434045</v>
       </c>
       <c r="B55" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6370,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R55" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6429,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6439,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,10 +6466,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432698</v>
+        <v>128437455</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,34 +6477,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R56" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6573,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128433166</v>
+        <v>128432659</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,34 +6584,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R57" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6643,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,12 +6653,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432985</v>
+        <v>128432698</v>
       </c>
       <c r="B58" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,34 +6691,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435046</v>
+        <v>434995</v>
       </c>
       <c r="R58" t="n">
-        <v>6786693</v>
+        <v>6786753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128437455</v>
+        <v>128432985</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434951</v>
+        <v>435046</v>
       </c>
       <c r="R59" t="n">
-        <v>6786479</v>
+        <v>6786693</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6897,7 +6897,7 @@
         <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>128433442</v>
       </c>
       <c r="B63" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7322,32 +7322,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437830</v>
+        <v>128434528</v>
       </c>
       <c r="B64" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434978</v>
+        <v>435062</v>
       </c>
       <c r="R64" t="n">
-        <v>6786579</v>
+        <v>6786456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128432598</v>
+        <v>128437830</v>
       </c>
       <c r="B65" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7460,14 +7460,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434985</v>
+        <v>434978</v>
       </c>
       <c r="R65" t="n">
-        <v>6786751</v>
+        <v>6786579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,45 +7536,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128434528</v>
+        <v>128432598</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435062</v>
+        <v>434985</v>
       </c>
       <c r="R66" t="n">
-        <v>6786456</v>
+        <v>6786751</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7646,7 +7646,7 @@
         <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7755,10 +7755,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128436694</v>
+        <v>128430389</v>
       </c>
       <c r="B68" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,34 +7766,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434968</v>
+        <v>434924</v>
       </c>
       <c r="R68" t="n">
-        <v>6786352</v>
+        <v>6786800</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7862,10 +7862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128433951</v>
+        <v>128433768</v>
       </c>
       <c r="B69" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,21 +7873,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435035</v>
+        <v>435033</v>
       </c>
       <c r="R69" t="n">
-        <v>6786547</v>
+        <v>6786548</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128430389</v>
+        <v>128437208</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,34 +7980,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434924</v>
+        <v>434976</v>
       </c>
       <c r="R70" t="n">
-        <v>6786800</v>
+        <v>6786430</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433768</v>
+        <v>128436694</v>
       </c>
       <c r="B71" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435033</v>
+        <v>434968</v>
       </c>
       <c r="R71" t="n">
-        <v>6786548</v>
+        <v>6786352</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128437208</v>
+        <v>128433951</v>
       </c>
       <c r="B72" t="n">
-        <v>78840</v>
+        <v>78845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434976</v>
+        <v>435035</v>
       </c>
       <c r="R72" t="n">
-        <v>6786430</v>
+        <v>6786547</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128437095</v>
+        <v>128434479</v>
       </c>
       <c r="B73" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434954</v>
+        <v>435046</v>
       </c>
       <c r="R73" t="n">
-        <v>6786401</v>
+        <v>6786473</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128433881</v>
+        <v>128437095</v>
       </c>
       <c r="B74" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8413,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435035</v>
+        <v>434954</v>
       </c>
       <c r="R74" t="n">
-        <v>6786547</v>
+        <v>6786401</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8472,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8482,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,10 +8509,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B75" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8520,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R75" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8579,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8611,10 +8616,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128438202</v>
+        <v>128437404</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8642,14 +8647,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435147</v>
+        <v>434956</v>
       </c>
       <c r="R76" t="n">
-        <v>6786737</v>
+        <v>6786459</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8681,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8691,12 +8696,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128434479</v>
+        <v>128438202</v>
       </c>
       <c r="B77" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8754,14 +8754,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435046</v>
+        <v>435147</v>
       </c>
       <c r="R77" t="n">
-        <v>6786473</v>
+        <v>6786737</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128452309</v>
+        <v>128434156</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8866,14 +8866,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434956</v>
+        <v>435002</v>
       </c>
       <c r="R78" t="n">
-        <v>6786830</v>
+        <v>6786518</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8915,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8945,7 +8950,7 @@
         <v>128438473</v>
       </c>
       <c r="B79" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9054,10 +9059,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,21 +9070,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B81" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,21 +9177,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R81" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,12 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435513</v>
+        <v>128452309</v>
       </c>
       <c r="B82" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435069</v>
+        <v>434956</v>
       </c>
       <c r="R82" t="n">
-        <v>6786320</v>
+        <v>6786830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128432486</v>
+        <v>128439136</v>
       </c>
       <c r="B83" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,14 +9411,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434985</v>
+        <v>435263</v>
       </c>
       <c r="R83" t="n">
-        <v>6786751</v>
+        <v>6786587</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430337</v>
+        <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434911</v>
+        <v>434985</v>
       </c>
       <c r="R84" t="n">
-        <v>6786789</v>
+        <v>6786751</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,10 +9594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128437508</v>
+        <v>128430113</v>
       </c>
       <c r="B85" t="n">
-        <v>78840</v>
+        <v>57686</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,34 +9605,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434949</v>
+        <v>434877</v>
       </c>
       <c r="R85" t="n">
-        <v>6786472</v>
+        <v>6786784</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9664,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9674,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9701,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128439136</v>
+        <v>128430337</v>
       </c>
       <c r="B86" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9732,14 +9737,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435263</v>
+        <v>434911</v>
       </c>
       <c r="R86" t="n">
-        <v>6786587</v>
+        <v>6786789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9771,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9781,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9808,10 +9813,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128430113</v>
+        <v>128437508</v>
       </c>
       <c r="B87" t="n">
-        <v>57682</v>
+        <v>78844</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9819,39 +9824,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434877</v>
+        <v>434949</v>
       </c>
       <c r="R87" t="n">
-        <v>6786784</v>
+        <v>6786472</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1351,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1361,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1424,7 +1419,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1463,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1473,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,45 +1500,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B10" t="n">
-        <v>79677</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R12" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R13" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3022,50 +3022,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128435386</v>
+        <v>128437687</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>78844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435059</v>
+        <v>434991</v>
       </c>
       <c r="R24" t="n">
-        <v>6786346</v>
+        <v>6786553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128430536</v>
+        <v>128437480</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,34 +3140,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434931</v>
+        <v>434949</v>
       </c>
       <c r="R25" t="n">
-        <v>6786802</v>
+        <v>6786475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,7 +3236,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437687</v>
+        <v>128436802</v>
       </c>
       <c r="B26" t="n">
         <v>78844</v>
@@ -3276,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434991</v>
+        <v>434960</v>
       </c>
       <c r="R26" t="n">
-        <v>6786553</v>
+        <v>6786370</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,45 +3343,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437480</v>
+        <v>128435386</v>
       </c>
       <c r="B27" t="n">
-        <v>79706</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434949</v>
+        <v>435059</v>
       </c>
       <c r="R27" t="n">
-        <v>6786475</v>
+        <v>6786346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128436802</v>
+        <v>128433812</v>
       </c>
       <c r="B28" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434960</v>
+        <v>435031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786370</v>
+        <v>6786549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,7 +3562,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128433812</v>
+        <v>128430536</v>
       </c>
       <c r="B29" t="n">
         <v>78845</v>
@@ -3593,14 +3593,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435031</v>
+        <v>434931</v>
       </c>
       <c r="R29" t="n">
-        <v>6786549</v>
+        <v>6786802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B30" t="n">
         <v>79087</v>
@@ -3700,14 +3700,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R30" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B31" t="n">
         <v>79087</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R31" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B32" t="n">
         <v>79087</v>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R32" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -7322,32 +7322,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128434528</v>
+        <v>128437830</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435062</v>
+        <v>434978</v>
       </c>
       <c r="R64" t="n">
-        <v>6786456</v>
+        <v>6786579</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,7 +7429,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437830</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
         <v>78845</v>
@@ -7460,14 +7460,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434978</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786579</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,45 +7536,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128432598</v>
+        <v>128434528</v>
       </c>
       <c r="B66" t="n">
-        <v>78845</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434985</v>
+        <v>435062</v>
       </c>
       <c r="R66" t="n">
-        <v>6786751</v>
+        <v>6786456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8835,7 +8835,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434156</v>
+        <v>128452309</v>
       </c>
       <c r="B78" t="n">
         <v>79087</v>
@@ -8866,14 +8866,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435002</v>
+        <v>434956</v>
       </c>
       <c r="R78" t="n">
-        <v>6786518</v>
+        <v>6786830</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,12 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,39 +8953,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9022,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9032,7 +9022,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128438473</v>
       </c>
       <c r="B80" t="n">
-        <v>78844</v>
+        <v>57686</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9070,34 +9065,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435172</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B81" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R81" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128452309</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434956</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786830</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>79677</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128431234</v>
+        <v>128438000</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434997</v>
+        <v>434956</v>
       </c>
       <c r="R8" t="n">
-        <v>6786800</v>
+        <v>6786742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,7 +1356,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1361,7 +1366,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128438000</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1419,7 +1424,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1428,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434956</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786742</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1473,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,50 +1505,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128432850</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435037</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786731</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
         <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128431612</v>
+        <v>128437383</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434923</v>
+        <v>434967</v>
       </c>
       <c r="R15" t="n">
-        <v>6786779</v>
+        <v>6786456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2124,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2134,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,45 +2161,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128438143</v>
+        <v>128435997</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435139</v>
+        <v>435005</v>
       </c>
       <c r="R16" t="n">
-        <v>6786742</v>
+        <v>6786307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2236,7 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437383</v>
+        <v>128438143</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,39 +2284,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434967</v>
+        <v>435139</v>
       </c>
       <c r="R17" t="n">
-        <v>6786456</v>
+        <v>6786742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437284</v>
+        <v>128431612</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,34 +2391,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434970</v>
+        <v>434923</v>
       </c>
       <c r="R18" t="n">
-        <v>6786443</v>
+        <v>6786779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2455,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437182</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434976</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786426</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2562,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,50 +2594,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128435997</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435005</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786307</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128430705</v>
+        <v>128433812</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,34 +2926,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434938</v>
+        <v>435031</v>
       </c>
       <c r="R23" t="n">
-        <v>6786813</v>
+        <v>6786549</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437687</v>
+        <v>128430536</v>
       </c>
       <c r="B24" t="n">
-        <v>78844</v>
+        <v>78847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434991</v>
+        <v>434931</v>
       </c>
       <c r="R24" t="n">
-        <v>6786553</v>
+        <v>6786802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,34 +3140,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R25" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,45 +3236,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128436802</v>
+        <v>128435386</v>
       </c>
       <c r="B26" t="n">
-        <v>78844</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434960</v>
+        <v>435059</v>
       </c>
       <c r="R26" t="n">
-        <v>6786370</v>
+        <v>6786346</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,50 +3348,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128435386</v>
+        <v>128437687</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435059</v>
+        <v>434991</v>
       </c>
       <c r="R27" t="n">
-        <v>6786346</v>
+        <v>6786553</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128433812</v>
+        <v>128437480</v>
       </c>
       <c r="B28" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435031</v>
+        <v>434949</v>
       </c>
       <c r="R28" t="n">
-        <v>6786549</v>
+        <v>6786475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128430536</v>
+        <v>128436802</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3573,34 +3573,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434931</v>
+        <v>434960</v>
       </c>
       <c r="R29" t="n">
-        <v>6786802</v>
+        <v>6786370</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,14 +3700,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R30" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R31" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R32" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3993,7 +3993,7 @@
         <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128439013</v>
+        <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435264</v>
+        <v>435043</v>
       </c>
       <c r="R34" t="n">
-        <v>6786618</v>
+        <v>6786691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4207,7 +4207,7 @@
         <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434019</v>
+        <v>128439013</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435020</v>
+        <v>435264</v>
       </c>
       <c r="R36" t="n">
-        <v>6786551</v>
+        <v>6786618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B37" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R37" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128432994</v>
+        <v>128434393</v>
       </c>
       <c r="B38" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435043</v>
+        <v>435046</v>
       </c>
       <c r="R38" t="n">
-        <v>6786691</v>
+        <v>6786471</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,7 +4635,7 @@
         <v>128436784</v>
       </c>
       <c r="B39" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>128437738</v>
       </c>
       <c r="B40" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>128438813</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437639</v>
+        <v>128431132</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434969</v>
+        <v>434976</v>
       </c>
       <c r="R43" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5135,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5140,7 +5145,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431132</v>
+        <v>128431219</v>
       </c>
       <c r="B44" t="n">
         <v>57686</v>
@@ -5207,7 +5212,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434976</v>
+        <v>434992</v>
       </c>
       <c r="R44" t="n">
         <v>6786804</v>
@@ -5242,7 +5247,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5257,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5284,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B45" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,39 +5295,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R45" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5394,7 +5394,7 @@
         <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128438534</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>435172</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786693</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128436819</v>
+        <v>128433488</v>
       </c>
       <c r="B51" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434960</v>
+        <v>435012</v>
       </c>
       <c r="R51" t="n">
-        <v>6786373</v>
+        <v>6786629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128433488</v>
+        <v>128436819</v>
       </c>
       <c r="B52" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435012</v>
+        <v>434960</v>
       </c>
       <c r="R52" t="n">
-        <v>6786629</v>
+        <v>6786373</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,7 +6143,7 @@
         <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128433166</v>
+        <v>128432698</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6278,14 +6278,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R54" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,12 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6359,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128434045</v>
+        <v>128433166</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6394,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R55" t="n">
-        <v>6786538</v>
+        <v>6786677</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6439,7 +6434,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6469,7 +6469,7 @@
         <v>128437455</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432659</v>
+        <v>128434045</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6584,34 +6584,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R57" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432698</v>
+        <v>128432659</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6790,7 +6790,7 @@
         <v>128432985</v>
       </c>
       <c r="B59" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,45 +7001,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128430267</v>
+        <v>128434528</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434893</v>
+        <v>435062</v>
       </c>
       <c r="R61" t="n">
-        <v>6786780</v>
+        <v>6786456</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437303</v>
+        <v>128432598</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>78847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434966</v>
+        <v>434985</v>
       </c>
       <c r="R62" t="n">
-        <v>6786443</v>
+        <v>6786751</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128433442</v>
+        <v>128437830</v>
       </c>
       <c r="B63" t="n">
-        <v>78844</v>
+        <v>78847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435015</v>
+        <v>434978</v>
       </c>
       <c r="R63" t="n">
-        <v>6786627</v>
+        <v>6786579</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437830</v>
+        <v>128430267</v>
       </c>
       <c r="B64" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,34 +7333,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434978</v>
+        <v>434893</v>
       </c>
       <c r="R64" t="n">
-        <v>6786579</v>
+        <v>6786780</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128432598</v>
+        <v>128437303</v>
       </c>
       <c r="B65" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434985</v>
+        <v>434966</v>
       </c>
       <c r="R65" t="n">
-        <v>6786751</v>
+        <v>6786443</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,32 +7536,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128434528</v>
+        <v>128433442</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435062</v>
+        <v>435015</v>
       </c>
       <c r="R66" t="n">
-        <v>6786456</v>
+        <v>6786627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7758,7 +7758,7 @@
         <v>128430389</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>128433768</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>128437208</v>
       </c>
       <c r="B70" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128436694</v>
+        <v>128433951</v>
       </c>
       <c r="B71" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434968</v>
+        <v>435035</v>
       </c>
       <c r="R71" t="n">
-        <v>6786352</v>
+        <v>6786547</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128433951</v>
+        <v>128436694</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435035</v>
+        <v>434968</v>
       </c>
       <c r="R72" t="n">
-        <v>6786547</v>
+        <v>6786352</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128434479</v>
+        <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435046</v>
+        <v>434954</v>
       </c>
       <c r="R73" t="n">
-        <v>6786473</v>
+        <v>6786401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,12 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8402,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128437095</v>
+        <v>128437404</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434954</v>
+        <v>434956</v>
       </c>
       <c r="R74" t="n">
-        <v>6786401</v>
+        <v>6786459</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8482,7 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8509,10 +8504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128433881</v>
+        <v>128438202</v>
       </c>
       <c r="B75" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8520,34 +8515,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435035</v>
+        <v>435147</v>
       </c>
       <c r="R75" t="n">
-        <v>6786547</v>
+        <v>6786737</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8574,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8589,7 +8584,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8616,10 +8616,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128437404</v>
+        <v>128434479</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434956</v>
+        <v>435046</v>
       </c>
       <c r="R76" t="n">
-        <v>6786459</v>
+        <v>6786473</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8696,7 +8696,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,10 +8728,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128438202</v>
+        <v>128433881</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8734,34 +8739,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435147</v>
+        <v>435035</v>
       </c>
       <c r="R77" t="n">
-        <v>6786737</v>
+        <v>6786547</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8798,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8808,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8838,7 +8838,7 @@
         <v>128452309</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8942,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,12 +9022,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B81" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,21 +9172,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9196,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R81" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B82" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128439136</v>
+        <v>128430113</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435263</v>
+        <v>434877</v>
       </c>
       <c r="R83" t="n">
-        <v>6786587</v>
+        <v>6786784</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9455,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9465,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9490,7 +9495,7 @@
         <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9594,10 +9599,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128430113</v>
+        <v>128430337</v>
       </c>
       <c r="B85" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,39 +9610,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434877</v>
+        <v>434911</v>
       </c>
       <c r="R85" t="n">
-        <v>6786784</v>
+        <v>6786789</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128430337</v>
+        <v>128439136</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9737,14 +9737,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434911</v>
+        <v>435263</v>
       </c>
       <c r="R86" t="n">
-        <v>6786789</v>
+        <v>6786587</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9816,7 +9816,7 @@
         <v>128437508</v>
       </c>
       <c r="B87" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,45 +1174,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128438000</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>434956</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1249,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,7 +1286,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128432850</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1312,7 +1317,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1321,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>435037</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1371,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,50 +1398,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128435467</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>435067</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437383</v>
+        <v>128431612</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,39 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434967</v>
+        <v>434923</v>
       </c>
       <c r="R15" t="n">
-        <v>6786456</v>
+        <v>6786779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,38 +2156,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R16" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128438143</v>
+        <v>128437284</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,34 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435139</v>
+        <v>434970</v>
       </c>
       <c r="R17" t="n">
-        <v>6786742</v>
+        <v>6786443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,7 +2375,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128431612</v>
+        <v>128438143</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2415,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434923</v>
+        <v>435139</v>
       </c>
       <c r="R18" t="n">
-        <v>6786779</v>
+        <v>6786742</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,45 +2482,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128435997</v>
       </c>
       <c r="B19" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>435005</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786307</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128430705</v>
+        <v>128437687</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,34 +3140,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434938</v>
+        <v>434991</v>
       </c>
       <c r="R25" t="n">
-        <v>6786813</v>
+        <v>6786553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,50 +3236,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128435386</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435059</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786346</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,7 +3343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437687</v>
+        <v>128436802</v>
       </c>
       <c r="B27" t="n">
         <v>78846</v>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434991</v>
+        <v>434960</v>
       </c>
       <c r="R27" t="n">
-        <v>6786553</v>
+        <v>6786370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B28" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,34 +3461,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R28" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,45 +3557,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128436802</v>
+        <v>128435386</v>
       </c>
       <c r="B29" t="n">
-        <v>78846</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434960</v>
+        <v>435059</v>
       </c>
       <c r="R29" t="n">
-        <v>6786370</v>
+        <v>6786346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431051</v>
+        <v>128431641</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434967</v>
+        <v>434924</v>
       </c>
       <c r="R30" t="n">
-        <v>6786800</v>
+        <v>6786755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R31" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R32" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128431641</v>
+        <v>128430028</v>
       </c>
       <c r="B33" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434924</v>
+        <v>434877</v>
       </c>
       <c r="R33" t="n">
-        <v>6786755</v>
+        <v>6786784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432994</v>
+        <v>128434019</v>
       </c>
       <c r="B34" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435043</v>
+        <v>435020</v>
       </c>
       <c r="R34" t="n">
-        <v>6786691</v>
+        <v>6786551</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128432204</v>
+        <v>128434393</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434949</v>
+        <v>435046</v>
       </c>
       <c r="R35" t="n">
-        <v>6786757</v>
+        <v>6786471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434019</v>
+        <v>128432204</v>
       </c>
       <c r="B37" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,34 +4429,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435020</v>
+        <v>434949</v>
       </c>
       <c r="R37" t="n">
-        <v>6786551</v>
+        <v>6786757</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128434393</v>
+        <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435046</v>
+        <v>435043</v>
       </c>
       <c r="R38" t="n">
-        <v>6786471</v>
+        <v>6786691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128431132</v>
+        <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434976</v>
+        <v>434969</v>
       </c>
       <c r="R43" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,7 +5130,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5145,7 +5140,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,7 +5167,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431219</v>
+        <v>128431132</v>
       </c>
       <c r="B44" t="n">
         <v>57686</v>
@@ -5212,7 +5207,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434992</v>
+        <v>434976</v>
       </c>
       <c r="R44" t="n">
         <v>6786804</v>
@@ -5247,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5257,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5284,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128437639</v>
+        <v>128431219</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5295,34 +5290,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434969</v>
+        <v>434992</v>
       </c>
       <c r="R45" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5712,7 +5712,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
         <v>79089</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128437246</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
         <v>79089</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434984</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786426</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128433488</v>
+        <v>128436819</v>
       </c>
       <c r="B51" t="n">
         <v>78847</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435012</v>
+        <v>434960</v>
       </c>
       <c r="R51" t="n">
-        <v>6786629</v>
+        <v>6786373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,7 +6033,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128436819</v>
+        <v>128433488</v>
       </c>
       <c r="B52" t="n">
         <v>78847</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434960</v>
+        <v>435012</v>
       </c>
       <c r="R52" t="n">
-        <v>6786373</v>
+        <v>6786629</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432698</v>
+        <v>128432659</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,21 +6258,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128433166</v>
+        <v>128432985</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435052</v>
+        <v>435046</v>
       </c>
       <c r="R55" t="n">
-        <v>6786677</v>
+        <v>6786693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,12 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6466,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128437455</v>
+        <v>128432698</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6477,34 +6472,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434951</v>
+        <v>434995</v>
       </c>
       <c r="R56" t="n">
-        <v>6786479</v>
+        <v>6786753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6546,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,7 +6568,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128434045</v>
+        <v>128433166</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6608,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435021</v>
+        <v>435052</v>
       </c>
       <c r="R57" t="n">
-        <v>6786538</v>
+        <v>6786677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6653,7 +6648,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432659</v>
+        <v>128434045</v>
       </c>
       <c r="B58" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,34 +6691,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R58" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,32 +6787,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128432985</v>
+        <v>128444055</v>
       </c>
       <c r="B59" t="n">
-        <v>79708</v>
+        <v>97462</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435046</v>
+        <v>435327</v>
       </c>
       <c r="R59" t="n">
-        <v>6786693</v>
+        <v>6786584</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128444055</v>
+        <v>128437455</v>
       </c>
       <c r="B60" t="n">
-        <v>97462</v>
+        <v>78847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435327</v>
+        <v>434951</v>
       </c>
       <c r="R60" t="n">
-        <v>6786584</v>
+        <v>6786479</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,45 +7001,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128434528</v>
+        <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435062</v>
+        <v>434893</v>
       </c>
       <c r="R61" t="n">
-        <v>6786456</v>
+        <v>6786780</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128432598</v>
+        <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434985</v>
+        <v>434966</v>
       </c>
       <c r="R62" t="n">
-        <v>6786751</v>
+        <v>6786443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128437830</v>
+        <v>128433442</v>
       </c>
       <c r="B63" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434978</v>
+        <v>435015</v>
       </c>
       <c r="R63" t="n">
-        <v>6786579</v>
+        <v>6786627</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128430267</v>
+        <v>128437830</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,34 +7333,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434893</v>
+        <v>434978</v>
       </c>
       <c r="R64" t="n">
-        <v>6786780</v>
+        <v>6786579</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437303</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434966</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786443</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,32 +7536,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128433442</v>
+        <v>128434528</v>
       </c>
       <c r="B66" t="n">
-        <v>78846</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435015</v>
+        <v>435062</v>
       </c>
       <c r="R66" t="n">
-        <v>6786627</v>
+        <v>6786456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128439118</v>
+        <v>128436694</v>
       </c>
       <c r="B67" t="n">
-        <v>57686</v>
+        <v>78847</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,39 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435271</v>
+        <v>434968</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7718,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7728,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128430389</v>
+        <v>128433951</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,34 +7761,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434924</v>
+        <v>435035</v>
       </c>
       <c r="R68" t="n">
-        <v>6786800</v>
+        <v>6786547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7835,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7969,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128437208</v>
+        <v>128430389</v>
       </c>
       <c r="B70" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,34 +7975,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434976</v>
+        <v>434924</v>
       </c>
       <c r="R70" t="n">
-        <v>6786430</v>
+        <v>6786800</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8044,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433951</v>
+        <v>128439118</v>
       </c>
       <c r="B71" t="n">
-        <v>78847</v>
+        <v>57686</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,34 +8082,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435035</v>
+        <v>435271</v>
       </c>
       <c r="R71" t="n">
-        <v>6786547</v>
+        <v>6786589</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128436694</v>
+        <v>128437208</v>
       </c>
       <c r="B72" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434968</v>
+        <v>434976</v>
       </c>
       <c r="R72" t="n">
-        <v>6786352</v>
+        <v>6786430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R74" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,7 +8504,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128438202</v>
+        <v>128437404</v>
       </c>
       <c r="B75" t="n">
         <v>79089</v>
@@ -8535,14 +8535,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435147</v>
+        <v>434956</v>
       </c>
       <c r="R75" t="n">
-        <v>6786737</v>
+        <v>6786459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,12 +8584,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8728,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128433881</v>
+        <v>128438202</v>
       </c>
       <c r="B77" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8739,34 +8734,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435035</v>
+        <v>435147</v>
       </c>
       <c r="R77" t="n">
-        <v>6786547</v>
+        <v>6786737</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8798,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8808,7 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,7 +8835,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128452309</v>
+        <v>128434156</v>
       </c>
       <c r="B78" t="n">
         <v>79089</v>
@@ -8866,14 +8866,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434956</v>
+        <v>435002</v>
       </c>
       <c r="R78" t="n">
-        <v>6786830</v>
+        <v>6786518</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8915,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B79" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8958,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8982,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,7 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9049,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128438473</v>
+        <v>128452309</v>
       </c>
       <c r="B80" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9060,39 +9065,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435172</v>
+        <v>434956</v>
       </c>
       <c r="R80" t="n">
-        <v>6786698</v>
+        <v>6786830</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128434156</v>
+        <v>128438473</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,34 +9172,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435002</v>
+        <v>435172</v>
       </c>
       <c r="R81" t="n">
-        <v>6786518</v>
+        <v>6786698</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,12 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435513</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435069</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786320</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,39 +9391,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R83" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9455,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9465,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128432486</v>
+        <v>128430113</v>
       </c>
       <c r="B84" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9503,34 +9498,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434985</v>
+        <v>434877</v>
       </c>
       <c r="R84" t="n">
-        <v>6786751</v>
+        <v>6786784</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9706,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128439136</v>
+        <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,21 +9717,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435263</v>
+        <v>434949</v>
       </c>
       <c r="R86" t="n">
-        <v>6786587</v>
+        <v>6786472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,10 +9813,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128437508</v>
+        <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434949</v>
+        <v>435263</v>
       </c>
       <c r="R87" t="n">
-        <v>6786472</v>
+        <v>6786587</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R9" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R12" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R13" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128431612</v>
+        <v>128437383</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434923</v>
+        <v>434967</v>
       </c>
       <c r="R15" t="n">
-        <v>6786779</v>
+        <v>6786456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2124,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2134,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437383</v>
+        <v>128431612</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,39 +2172,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434967</v>
+        <v>434923</v>
       </c>
       <c r="R16" t="n">
-        <v>6786456</v>
+        <v>6786779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437284</v>
+        <v>128438143</v>
       </c>
       <c r="B17" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,34 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434970</v>
+        <v>435139</v>
       </c>
       <c r="R17" t="n">
-        <v>6786443</v>
+        <v>6786742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,45 +2375,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128438143</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435139</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786742</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2455,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,50 +2487,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128435997</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435005</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786307</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128433812</v>
+        <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435031</v>
+        <v>434991</v>
       </c>
       <c r="R23" t="n">
-        <v>6786549</v>
+        <v>6786553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128430536</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434931</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786802</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437687</v>
+        <v>128436802</v>
       </c>
       <c r="B25" t="n">
         <v>78846</v>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434991</v>
+        <v>434960</v>
       </c>
       <c r="R25" t="n">
-        <v>6786553</v>
+        <v>6786370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,45 +3343,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128436802</v>
+        <v>128435386</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434960</v>
+        <v>435059</v>
       </c>
       <c r="R27" t="n">
-        <v>6786370</v>
+        <v>6786346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430705</v>
+        <v>128433812</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,34 +3466,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434938</v>
+        <v>435031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786813</v>
+        <v>6786549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,50 +3562,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128435386</v>
+        <v>128430536</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435059</v>
+        <v>434931</v>
       </c>
       <c r="R29" t="n">
-        <v>6786346</v>
+        <v>6786802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431641</v>
+        <v>128447259</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434924</v>
+        <v>435291</v>
       </c>
       <c r="R30" t="n">
-        <v>6786755</v>
+        <v>6786596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R31" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R32" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128430028</v>
+        <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434877</v>
+        <v>434924</v>
       </c>
       <c r="R33" t="n">
-        <v>6786784</v>
+        <v>6786755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432659</v>
+        <v>128437455</v>
       </c>
       <c r="B54" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R54" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,32 +6354,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432985</v>
+        <v>128444055</v>
       </c>
       <c r="B55" t="n">
-        <v>79708</v>
+        <v>97462</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435046</v>
+        <v>435327</v>
       </c>
       <c r="R55" t="n">
-        <v>6786693</v>
+        <v>6786584</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,45 +6787,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128444055</v>
+        <v>128432659</v>
       </c>
       <c r="B59" t="n">
-        <v>97462</v>
+        <v>79708</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435327</v>
+        <v>434995</v>
       </c>
       <c r="R59" t="n">
-        <v>6786584</v>
+        <v>6786753</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128437455</v>
+        <v>128432985</v>
       </c>
       <c r="B60" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6905,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434951</v>
+        <v>435046</v>
       </c>
       <c r="R60" t="n">
-        <v>6786479</v>
+        <v>6786693</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128430267</v>
+        <v>128432598</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434893</v>
+        <v>434985</v>
       </c>
       <c r="R61" t="n">
-        <v>6786780</v>
+        <v>6786751</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437303</v>
+        <v>128437830</v>
       </c>
       <c r="B62" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434966</v>
+        <v>434978</v>
       </c>
       <c r="R62" t="n">
-        <v>6786443</v>
+        <v>6786579</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128433442</v>
+        <v>128430267</v>
       </c>
       <c r="B63" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,34 +7226,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435015</v>
+        <v>434893</v>
       </c>
       <c r="R63" t="n">
-        <v>6786627</v>
+        <v>6786780</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437830</v>
+        <v>128437303</v>
       </c>
       <c r="B64" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434978</v>
+        <v>434966</v>
       </c>
       <c r="R64" t="n">
-        <v>6786579</v>
+        <v>6786443</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128432598</v>
+        <v>128433442</v>
       </c>
       <c r="B65" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434985</v>
+        <v>435015</v>
       </c>
       <c r="R65" t="n">
-        <v>6786751</v>
+        <v>6786627</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434156</v>
+        <v>128438473</v>
       </c>
       <c r="B78" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,34 +8846,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435002</v>
+        <v>435172</v>
       </c>
       <c r="R78" t="n">
-        <v>6786518</v>
+        <v>6786698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,12 +8920,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435513</v>
+        <v>128452309</v>
       </c>
       <c r="B79" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,34 +8958,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435069</v>
+        <v>434956</v>
       </c>
       <c r="R79" t="n">
-        <v>6786320</v>
+        <v>6786830</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128452309</v>
+        <v>128435643</v>
       </c>
       <c r="B80" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,34 +9065,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434956</v>
+        <v>435049</v>
       </c>
       <c r="R80" t="n">
-        <v>6786830</v>
+        <v>6786296</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B81" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,39 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R81" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128435513</v>
       </c>
       <c r="B82" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>435069</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786320</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,34 +1409,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R9" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R12" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R13" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437383</v>
+        <v>128431612</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,39 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434967</v>
+        <v>434923</v>
       </c>
       <c r="R15" t="n">
-        <v>6786456</v>
+        <v>6786779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128431612</v>
+        <v>128438143</v>
       </c>
       <c r="B16" t="n">
         <v>79089</v>
@@ -2196,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434923</v>
+        <v>435139</v>
       </c>
       <c r="R16" t="n">
-        <v>6786779</v>
+        <v>6786742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128438143</v>
+        <v>128437383</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435139</v>
+        <v>434967</v>
       </c>
       <c r="R17" t="n">
-        <v>6786742</v>
+        <v>6786456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,50 +2375,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437284</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434970</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786443</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2482,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128437182</v>
       </c>
       <c r="B19" t="n">
         <v>78847</v>
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>434976</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2552,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2562,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,45 +2589,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128435997</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>435005</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128437687</v>
+        <v>128430536</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,34 +2926,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434991</v>
+        <v>434931</v>
       </c>
       <c r="R23" t="n">
-        <v>6786553</v>
+        <v>6786802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437480</v>
+        <v>128437687</v>
       </c>
       <c r="B24" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434949</v>
+        <v>434991</v>
       </c>
       <c r="R24" t="n">
-        <v>6786475</v>
+        <v>6786553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128430705</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434938</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786813</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,50 +3343,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128435386</v>
+        <v>128430705</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435059</v>
+        <v>434938</v>
       </c>
       <c r="R27" t="n">
-        <v>6786346</v>
+        <v>6786813</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,45 +3450,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128433812</v>
+        <v>128435386</v>
       </c>
       <c r="B28" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435031</v>
+        <v>435059</v>
       </c>
       <c r="R28" t="n">
-        <v>6786549</v>
+        <v>6786346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,7 +3562,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128430536</v>
+        <v>128433812</v>
       </c>
       <c r="B29" t="n">
         <v>78847</v>
@@ -3593,14 +3593,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434931</v>
+        <v>435031</v>
       </c>
       <c r="R29" t="n">
-        <v>6786802</v>
+        <v>6786549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128447259</v>
+        <v>128431641</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435291</v>
+        <v>434924</v>
       </c>
       <c r="R30" t="n">
-        <v>6786596</v>
+        <v>6786755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R31" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R32" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128431641</v>
+        <v>128431051</v>
       </c>
       <c r="B33" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434924</v>
+        <v>434967</v>
       </c>
       <c r="R33" t="n">
-        <v>6786755</v>
+        <v>6786800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128434019</v>
+        <v>128439013</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435020</v>
+        <v>435264</v>
       </c>
       <c r="R34" t="n">
-        <v>6786551</v>
+        <v>6786618</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,7 +4204,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B35" t="n">
         <v>78846</v>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R35" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128439013</v>
+        <v>128434393</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435264</v>
+        <v>435046</v>
       </c>
       <c r="R36" t="n">
-        <v>6786618</v>
+        <v>6786471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128436819</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>434960</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128431782</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,34 +5830,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>434911</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128436819</v>
+        <v>128433488</v>
       </c>
       <c r="B51" t="n">
         <v>78847</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434960</v>
+        <v>435012</v>
       </c>
       <c r="R51" t="n">
-        <v>6786373</v>
+        <v>6786629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128433488</v>
+        <v>128437246</v>
       </c>
       <c r="B52" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435012</v>
+        <v>434984</v>
       </c>
       <c r="R52" t="n">
-        <v>6786629</v>
+        <v>6786426</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128431782</v>
+        <v>128438534</v>
       </c>
       <c r="B53" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434911</v>
+        <v>435172</v>
       </c>
       <c r="R53" t="n">
-        <v>6786765</v>
+        <v>6786693</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128437455</v>
+        <v>128432698</v>
       </c>
       <c r="B54" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434951</v>
+        <v>434995</v>
       </c>
       <c r="R54" t="n">
-        <v>6786479</v>
+        <v>6786753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,32 +6354,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128444055</v>
+        <v>128433166</v>
       </c>
       <c r="B55" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435327</v>
+        <v>435052</v>
       </c>
       <c r="R55" t="n">
-        <v>6786584</v>
+        <v>6786677</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,7 +6466,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432698</v>
+        <v>128434045</v>
       </c>
       <c r="B56" t="n">
         <v>79089</v>
@@ -6492,14 +6497,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R56" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6573,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128433166</v>
+        <v>128432985</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,21 +6584,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6603,10 +6608,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435052</v>
+        <v>435046</v>
       </c>
       <c r="R57" t="n">
-        <v>6786677</v>
+        <v>6786693</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6643,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,12 +6653,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128434045</v>
+        <v>128432659</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,34 +6691,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435021</v>
+        <v>434995</v>
       </c>
       <c r="R58" t="n">
-        <v>6786538</v>
+        <v>6786753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,45 +6787,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128432659</v>
+        <v>128444055</v>
       </c>
       <c r="B59" t="n">
-        <v>79708</v>
+        <v>97463</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434995</v>
+        <v>435327</v>
       </c>
       <c r="R59" t="n">
-        <v>6786753</v>
+        <v>6786584</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128432985</v>
+        <v>128437455</v>
       </c>
       <c r="B60" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6905,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435046</v>
+        <v>434951</v>
       </c>
       <c r="R60" t="n">
-        <v>6786693</v>
+        <v>6786479</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128432598</v>
+        <v>128433442</v>
       </c>
       <c r="B61" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434985</v>
+        <v>435015</v>
       </c>
       <c r="R61" t="n">
-        <v>6786751</v>
+        <v>6786627</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437830</v>
+        <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434978</v>
+        <v>434966</v>
       </c>
       <c r="R62" t="n">
-        <v>6786579</v>
+        <v>6786443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437303</v>
+        <v>128437830</v>
       </c>
       <c r="B64" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434966</v>
+        <v>434978</v>
       </c>
       <c r="R64" t="n">
-        <v>6786443</v>
+        <v>6786579</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128433442</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435015</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786627</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128436694</v>
+        <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>78847</v>
+        <v>57686</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434968</v>
+        <v>435271</v>
       </c>
       <c r="R67" t="n">
-        <v>6786352</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7755,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433951</v>
+        <v>128433768</v>
       </c>
       <c r="B68" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,21 +7766,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435035</v>
+        <v>435033</v>
       </c>
       <c r="R68" t="n">
-        <v>6786547</v>
+        <v>6786548</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7835,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128433768</v>
+        <v>128437208</v>
       </c>
       <c r="B69" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,21 +7873,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7892,10 +7897,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435033</v>
+        <v>434976</v>
       </c>
       <c r="R69" t="n">
-        <v>6786548</v>
+        <v>6786430</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128439118</v>
+        <v>128433951</v>
       </c>
       <c r="B71" t="n">
-        <v>57686</v>
+        <v>78847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,39 +8087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435271</v>
+        <v>435035</v>
       </c>
       <c r="R71" t="n">
-        <v>6786589</v>
+        <v>6786547</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128437208</v>
+        <v>128436694</v>
       </c>
       <c r="B72" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434976</v>
+        <v>434968</v>
       </c>
       <c r="R72" t="n">
-        <v>6786430</v>
+        <v>6786352</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,7 +8290,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128437095</v>
+        <v>128438202</v>
       </c>
       <c r="B73" t="n">
         <v>79089</v>
@@ -8321,14 +8321,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434954</v>
+        <v>435147</v>
       </c>
       <c r="R73" t="n">
-        <v>6786401</v>
+        <v>6786737</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128433881</v>
+        <v>128437404</v>
       </c>
       <c r="B74" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8413,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435035</v>
+        <v>434956</v>
       </c>
       <c r="R74" t="n">
-        <v>6786547</v>
+        <v>6786459</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8472,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8482,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,10 +8509,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8520,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R75" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8579,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8611,7 +8616,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128434479</v>
+        <v>128437095</v>
       </c>
       <c r="B76" t="n">
         <v>79089</v>
@@ -8646,10 +8651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435046</v>
+        <v>434954</v>
       </c>
       <c r="R76" t="n">
-        <v>6786473</v>
+        <v>6786401</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8681,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8691,12 +8696,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,7 +8723,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128438202</v>
+        <v>128434479</v>
       </c>
       <c r="B77" t="n">
         <v>79089</v>
@@ -8754,14 +8754,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435147</v>
+        <v>435046</v>
       </c>
       <c r="R77" t="n">
-        <v>6786737</v>
+        <v>6786473</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B78" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,39 +8846,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R78" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8910,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8920,7 +8915,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128452309</v>
+        <v>128435513</v>
       </c>
       <c r="B79" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,34 +8958,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434956</v>
+        <v>435069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786830</v>
+        <v>6786320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435643</v>
+        <v>128438473</v>
       </c>
       <c r="B80" t="n">
-        <v>78847</v>
+        <v>57686</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,34 +9065,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435049</v>
+        <v>435172</v>
       </c>
       <c r="R80" t="n">
-        <v>6786296</v>
+        <v>6786698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,7 +9166,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128434156</v>
+        <v>128452309</v>
       </c>
       <c r="B81" t="n">
         <v>79089</v>
@@ -9192,14 +9197,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435002</v>
+        <v>434956</v>
       </c>
       <c r="R81" t="n">
-        <v>6786518</v>
+        <v>6786830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,12 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435513</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435069</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786320</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,7 +9380,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128432486</v>
+        <v>128439136</v>
       </c>
       <c r="B83" t="n">
         <v>79089</v>
@@ -9411,14 +9411,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434985</v>
+        <v>435263</v>
       </c>
       <c r="R83" t="n">
-        <v>6786751</v>
+        <v>6786587</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430113</v>
+        <v>128437508</v>
       </c>
       <c r="B84" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9498,39 +9498,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434877</v>
+        <v>434949</v>
       </c>
       <c r="R84" t="n">
-        <v>6786784</v>
+        <v>6786472</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9572,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,7 +9594,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128430337</v>
+        <v>128432486</v>
       </c>
       <c r="B85" t="n">
         <v>79089</v>
@@ -9634,10 +9629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434911</v>
+        <v>434985</v>
       </c>
       <c r="R85" t="n">
-        <v>6786789</v>
+        <v>6786751</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9664,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9674,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,10 +9701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128437508</v>
+        <v>128430337</v>
       </c>
       <c r="B86" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,34 +9712,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434949</v>
+        <v>434911</v>
       </c>
       <c r="R86" t="n">
-        <v>6786472</v>
+        <v>6786789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9771,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9781,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,10 +9808,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128439136</v>
+        <v>128430113</v>
       </c>
       <c r="B87" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9824,34 +9819,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435263</v>
+        <v>434877</v>
       </c>
       <c r="R87" t="n">
-        <v>6786587</v>
+        <v>6786784</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,50 +1174,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1317,7 +1312,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1326,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R8" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1356,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1371,7 +1366,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,45 +1393,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -8402,7 +8402,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128437404</v>
+        <v>128434479</v>
       </c>
       <c r="B74" t="n">
         <v>79089</v>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434956</v>
+        <v>435046</v>
       </c>
       <c r="R74" t="n">
-        <v>6786459</v>
+        <v>6786473</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8482,7 +8482,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8509,10 +8514,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128433881</v>
+        <v>128437404</v>
       </c>
       <c r="B75" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8520,21 +8525,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8544,10 +8549,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435035</v>
+        <v>434956</v>
       </c>
       <c r="R75" t="n">
-        <v>6786547</v>
+        <v>6786459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8584,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8589,7 +8594,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8616,10 +8621,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128437095</v>
+        <v>128433881</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8627,21 +8632,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434954</v>
+        <v>435035</v>
       </c>
       <c r="R76" t="n">
-        <v>6786401</v>
+        <v>6786547</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8686,7 +8691,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8696,7 +8701,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,7 +8728,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128434479</v>
+        <v>128437095</v>
       </c>
       <c r="B77" t="n">
         <v>79089</v>
@@ -8758,10 +8763,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435046</v>
+        <v>434954</v>
       </c>
       <c r="R77" t="n">
-        <v>6786473</v>
+        <v>6786401</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8798,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8808,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,7 +8835,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434156</v>
+        <v>128452309</v>
       </c>
       <c r="B78" t="n">
         <v>79089</v>
@@ -8866,14 +8866,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435002</v>
+        <v>434956</v>
       </c>
       <c r="R78" t="n">
-        <v>6786518</v>
+        <v>6786830</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,12 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435513</v>
+        <v>128435643</v>
       </c>
       <c r="B79" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,21 +8953,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8982,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435069</v>
+        <v>435049</v>
       </c>
       <c r="R79" t="n">
-        <v>6786320</v>
+        <v>6786296</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9022,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9049,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B80" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,39 +9060,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R80" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9129,7 +9119,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9139,7 +9129,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128452309</v>
+        <v>128435513</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,34 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434956</v>
+        <v>435069</v>
       </c>
       <c r="R81" t="n">
-        <v>6786830</v>
+        <v>6786320</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9268,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128438473</v>
       </c>
       <c r="B82" t="n">
-        <v>78847</v>
+        <v>57686</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9279,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>435172</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786698</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>128432333</v>
       </c>
       <c r="B90" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>128526361</v>
       </c>
       <c r="B91" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>128440167</v>
       </c>
       <c r="B92" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1177,7 +1177,7 @@
         <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>128435686</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R12" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R13" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128431612</v>
+        <v>128438143</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434923</v>
+        <v>435139</v>
       </c>
       <c r="R15" t="n">
-        <v>6786779</v>
+        <v>6786742</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128438143</v>
+        <v>128431612</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435139</v>
+        <v>434923</v>
       </c>
       <c r="R16" t="n">
-        <v>6786742</v>
+        <v>6786779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,7 +2266,7 @@
         <v>128437383</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,45 +2375,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437284</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434970</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786443</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2455,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437182</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434976</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786426</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2562,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,50 +2594,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128435997</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78874</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435005</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786307</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128430536</v>
+        <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,34 +2926,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434931</v>
+        <v>434991</v>
       </c>
       <c r="R23" t="n">
-        <v>6786802</v>
+        <v>6786553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437687</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>79735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434991</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786553</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,7 +3132,7 @@
         <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,45 +3343,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128430705</v>
+        <v>128435386</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434938</v>
+        <v>435059</v>
       </c>
       <c r="R27" t="n">
-        <v>6786813</v>
+        <v>6786346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,50 +3455,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128435386</v>
+        <v>128433812</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>78874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435059</v>
+        <v>435031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786346</v>
+        <v>6786549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128433812</v>
+        <v>128430536</v>
       </c>
       <c r="B29" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,14 +3593,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435031</v>
+        <v>434931</v>
       </c>
       <c r="R29" t="n">
-        <v>6786549</v>
+        <v>6786802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431641</v>
+        <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434924</v>
+        <v>434967</v>
       </c>
       <c r="R30" t="n">
-        <v>6786755</v>
+        <v>6786800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,7 +3779,7 @@
         <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128431051</v>
+        <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434967</v>
+        <v>434924</v>
       </c>
       <c r="R33" t="n">
-        <v>6786800</v>
+        <v>6786755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128439013</v>
+        <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435264</v>
+        <v>435043</v>
       </c>
       <c r="R34" t="n">
-        <v>6786618</v>
+        <v>6786691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434019</v>
+        <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435020</v>
+        <v>434949</v>
       </c>
       <c r="R35" t="n">
-        <v>6786551</v>
+        <v>6786757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B36" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R36" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128432204</v>
+        <v>128434393</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,34 +4429,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434949</v>
+        <v>435046</v>
       </c>
       <c r="R37" t="n">
-        <v>6786757</v>
+        <v>6786471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128432994</v>
+        <v>128439013</v>
       </c>
       <c r="B38" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435043</v>
+        <v>435264</v>
       </c>
       <c r="R38" t="n">
-        <v>6786691</v>
+        <v>6786618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,7 +4635,7 @@
         <v>128436784</v>
       </c>
       <c r="B39" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>128437738</v>
       </c>
       <c r="B40" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>128438813</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437639</v>
+        <v>128431132</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434969</v>
+        <v>434976</v>
       </c>
       <c r="R43" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5135,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5140,7 +5145,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431132</v>
+        <v>128431219</v>
       </c>
       <c r="B44" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,7 +5212,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434976</v>
+        <v>434992</v>
       </c>
       <c r="R44" t="n">
         <v>6786804</v>
@@ -5242,7 +5247,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5257,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5284,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B45" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,39 +5295,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R45" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5394,7 +5394,7 @@
         <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128436819</v>
+        <v>128433488</v>
       </c>
       <c r="B49" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434960</v>
+        <v>435012</v>
       </c>
       <c r="R49" t="n">
-        <v>6786373</v>
+        <v>6786629</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128431782</v>
+        <v>128436819</v>
       </c>
       <c r="B50" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5850,14 +5850,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434911</v>
+        <v>434960</v>
       </c>
       <c r="R50" t="n">
-        <v>6786765</v>
+        <v>6786373</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128433488</v>
+        <v>128431782</v>
       </c>
       <c r="B51" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435012</v>
+        <v>434911</v>
       </c>
       <c r="R51" t="n">
-        <v>6786629</v>
+        <v>6786765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6036,7 +6036,7 @@
         <v>128437246</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>128438534</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432698</v>
+        <v>128434045</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6278,14 +6278,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R54" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128433166</v>
+        <v>128432659</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R55" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,12 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6466,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128434045</v>
+        <v>128432698</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6497,14 +6492,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435021</v>
+        <v>434995</v>
       </c>
       <c r="R56" t="n">
-        <v>6786538</v>
+        <v>6786753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6546,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432985</v>
+        <v>128433166</v>
       </c>
       <c r="B57" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6584,21 +6579,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6608,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435046</v>
+        <v>435052</v>
       </c>
       <c r="R57" t="n">
-        <v>6786693</v>
+        <v>6786677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6653,7 +6648,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432659</v>
+        <v>128432985</v>
       </c>
       <c r="B58" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,14 +6711,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434995</v>
+        <v>435046</v>
       </c>
       <c r="R58" t="n">
-        <v>6786753</v>
+        <v>6786693</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6790,7 +6790,7 @@
         <v>128444055</v>
       </c>
       <c r="B59" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128437455</v>
       </c>
       <c r="B60" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128433442</v>
+        <v>128432598</v>
       </c>
       <c r="B61" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435015</v>
+        <v>434985</v>
       </c>
       <c r="R61" t="n">
-        <v>6786627</v>
+        <v>6786751</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437303</v>
+        <v>128437830</v>
       </c>
       <c r="B62" t="n">
-        <v>79708</v>
+        <v>78874</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434966</v>
+        <v>434978</v>
       </c>
       <c r="R62" t="n">
-        <v>6786443</v>
+        <v>6786579</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7218,7 +7218,7 @@
         <v>128430267</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437830</v>
+        <v>128437303</v>
       </c>
       <c r="B64" t="n">
-        <v>78847</v>
+        <v>79735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434978</v>
+        <v>434966</v>
       </c>
       <c r="R64" t="n">
-        <v>6786579</v>
+        <v>6786443</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128432598</v>
+        <v>128433442</v>
       </c>
       <c r="B65" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,34 +7440,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434985</v>
+        <v>435015</v>
       </c>
       <c r="R65" t="n">
-        <v>6786751</v>
+        <v>6786627</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128439118</v>
+        <v>128430389</v>
       </c>
       <c r="B67" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,39 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435271</v>
+        <v>434924</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786800</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7718,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7728,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7758,7 +7753,7 @@
         <v>128433768</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7865,7 +7860,7 @@
         <v>128437208</v>
       </c>
       <c r="B69" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7969,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128430389</v>
+        <v>128439118</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,34 +7975,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434924</v>
+        <v>435271</v>
       </c>
       <c r="R70" t="n">
-        <v>6786800</v>
+        <v>6786589</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8079,7 +8079,7 @@
         <v>128433951</v>
       </c>
       <c r="B71" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>128436694</v>
       </c>
       <c r="B72" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128438202</v>
+        <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8321,14 +8321,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435147</v>
+        <v>434954</v>
       </c>
       <c r="R73" t="n">
-        <v>6786737</v>
+        <v>6786401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,12 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8402,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128434479</v>
+        <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8413,21 +8408,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435046</v>
+        <v>435035</v>
       </c>
       <c r="R74" t="n">
-        <v>6786473</v>
+        <v>6786547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8482,12 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8517,7 +8507,7 @@
         <v>128437404</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8621,10 +8611,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128433881</v>
+        <v>128438202</v>
       </c>
       <c r="B76" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8632,34 +8622,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435035</v>
+        <v>435147</v>
       </c>
       <c r="R76" t="n">
-        <v>6786547</v>
+        <v>6786737</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8691,7 +8681,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8701,7 +8691,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8728,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128437095</v>
+        <v>128434479</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8763,10 +8758,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434954</v>
+        <v>435046</v>
       </c>
       <c r="R77" t="n">
-        <v>6786401</v>
+        <v>6786473</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8798,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8808,7 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128452309</v>
+        <v>128435643</v>
       </c>
       <c r="B78" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,34 +8846,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434956</v>
+        <v>435049</v>
       </c>
       <c r="R78" t="n">
-        <v>6786830</v>
+        <v>6786296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435643</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435049</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786296</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,7 +9022,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9049,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9060,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9084,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9119,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9129,12 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435513</v>
+        <v>128452309</v>
       </c>
       <c r="B81" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,34 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435069</v>
+        <v>434956</v>
       </c>
       <c r="R81" t="n">
-        <v>6786320</v>
+        <v>6786830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9271,7 +9271,7 @@
         <v>128438473</v>
       </c>
       <c r="B82" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128439136</v>
+        <v>128432486</v>
       </c>
       <c r="B83" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,14 +9411,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435263</v>
+        <v>434985</v>
       </c>
       <c r="R83" t="n">
-        <v>6786587</v>
+        <v>6786751</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128437508</v>
+        <v>128430337</v>
       </c>
       <c r="B84" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9498,34 +9498,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434949</v>
+        <v>434911</v>
       </c>
       <c r="R84" t="n">
-        <v>6786472</v>
+        <v>6786789</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,10 +9594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128432486</v>
+        <v>128437508</v>
       </c>
       <c r="B85" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,34 +9605,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434985</v>
+        <v>434949</v>
       </c>
       <c r="R85" t="n">
-        <v>6786751</v>
+        <v>6786472</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9701,10 +9701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128430337</v>
+        <v>128439136</v>
       </c>
       <c r="B86" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9732,14 +9732,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434911</v>
+        <v>435263</v>
       </c>
       <c r="R86" t="n">
-        <v>6786789</v>
+        <v>6786587</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9811,7 +9811,7 @@
         <v>128430113</v>
       </c>
       <c r="B87" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,45 +1174,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128438000</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>434956</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1249,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,7 +1286,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128432850</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1312,7 +1317,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1321,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>435037</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1371,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,50 +1398,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128435467</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>435067</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128433488</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435012</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786629</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128436819</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434960</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786373</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128431782</v>
+        <v>128436819</v>
       </c>
       <c r="B51" t="n">
         <v>78874</v>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434911</v>
+        <v>434960</v>
       </c>
       <c r="R51" t="n">
-        <v>6786765</v>
+        <v>6786373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128437246</v>
+        <v>128433488</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434984</v>
+        <v>435012</v>
       </c>
       <c r="R52" t="n">
-        <v>6786426</v>
+        <v>6786629</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128438534</v>
+        <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435172</v>
+        <v>434911</v>
       </c>
       <c r="R53" t="n">
-        <v>6786693</v>
+        <v>6786765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6787,32 +6787,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128444055</v>
+        <v>128437455</v>
       </c>
       <c r="B59" t="n">
-        <v>97490</v>
+        <v>78874</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435327</v>
+        <v>434951</v>
       </c>
       <c r="R59" t="n">
-        <v>6786584</v>
+        <v>6786479</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128437455</v>
+        <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>78874</v>
+        <v>97490</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434951</v>
+        <v>435327</v>
       </c>
       <c r="R60" t="n">
-        <v>6786479</v>
+        <v>6786584</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,7 +7001,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128432598</v>
+        <v>128437830</v>
       </c>
       <c r="B61" t="n">
         <v>78874</v>
@@ -7032,14 +7032,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434985</v>
+        <v>434978</v>
       </c>
       <c r="R61" t="n">
-        <v>6786751</v>
+        <v>6786579</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,7 +7108,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437830</v>
+        <v>128432598</v>
       </c>
       <c r="B62" t="n">
         <v>78874</v>
@@ -7139,14 +7139,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434978</v>
+        <v>434985</v>
       </c>
       <c r="R62" t="n">
-        <v>6786579</v>
+        <v>6786751</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128430389</v>
+        <v>128436694</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434924</v>
+        <v>434968</v>
       </c>
       <c r="R67" t="n">
-        <v>6786800</v>
+        <v>6786352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433768</v>
+        <v>128433951</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,21 +7761,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435033</v>
+        <v>435035</v>
       </c>
       <c r="R68" t="n">
-        <v>6786548</v>
+        <v>6786547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128437208</v>
+        <v>128430389</v>
       </c>
       <c r="B69" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,34 +7868,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434976</v>
+        <v>434924</v>
       </c>
       <c r="R69" t="n">
-        <v>6786430</v>
+        <v>6786800</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128439118</v>
+        <v>128433768</v>
       </c>
       <c r="B70" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,39 +7975,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435271</v>
+        <v>435033</v>
       </c>
       <c r="R70" t="n">
-        <v>6786589</v>
+        <v>6786548</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8044,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433951</v>
+        <v>128437208</v>
       </c>
       <c r="B71" t="n">
-        <v>78874</v>
+        <v>78873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,21 +8082,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435035</v>
+        <v>434976</v>
       </c>
       <c r="R71" t="n">
-        <v>6786547</v>
+        <v>6786430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8141,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8151,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8178,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128436694</v>
+        <v>128439118</v>
       </c>
       <c r="B72" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,34 +8189,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434968</v>
+        <v>435271</v>
       </c>
       <c r="R72" t="n">
-        <v>6786352</v>
+        <v>6786589</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128435643</v>
+        <v>128434156</v>
       </c>
       <c r="B78" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435049</v>
+        <v>435002</v>
       </c>
       <c r="R78" t="n">
-        <v>6786296</v>
+        <v>6786518</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8915,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8958,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8982,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,12 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128438473</v>
       </c>
       <c r="B80" t="n">
-        <v>78873</v>
+        <v>57713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,34 +9065,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435172</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128452309</v>
+        <v>128435643</v>
       </c>
       <c r="B81" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,34 +9177,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434956</v>
+        <v>435049</v>
       </c>
       <c r="R81" t="n">
-        <v>6786830</v>
+        <v>6786296</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9268,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128438473</v>
+        <v>128452309</v>
       </c>
       <c r="B82" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9279,39 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435172</v>
+        <v>434956</v>
       </c>
       <c r="R82" t="n">
-        <v>6786698</v>
+        <v>6786830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,50 +1174,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,45 +1393,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128435467</v>
+        <v>128438000</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435067</v>
+        <v>434956</v>
       </c>
       <c r="R9" t="n">
-        <v>6786325</v>
+        <v>6786742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128437673</v>
+        <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,34 +1739,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434991</v>
+        <v>434953</v>
       </c>
       <c r="R12" t="n">
-        <v>6786554</v>
+        <v>6786800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128430866</v>
+        <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434953</v>
+        <v>434991</v>
       </c>
       <c r="R13" t="n">
-        <v>6786800</v>
+        <v>6786554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>128438143</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>128431612</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437383</v>
+        <v>128437284</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,39 +2274,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434967</v>
+        <v>434970</v>
       </c>
       <c r="R17" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,50 +2370,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437182</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434976</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786426</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2440,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2450,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128437383</v>
       </c>
       <c r="B19" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2488,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>434967</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786456</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2552,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2562,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,45 +2589,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128435997</v>
       </c>
       <c r="B20" t="n">
-        <v>78874</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>435005</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437480</v>
+        <v>128436802</v>
       </c>
       <c r="B24" t="n">
-        <v>79735</v>
+        <v>78877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434949</v>
+        <v>434960</v>
       </c>
       <c r="R24" t="n">
-        <v>6786475</v>
+        <v>6786370</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128436802</v>
+        <v>128430705</v>
       </c>
       <c r="B25" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,34 +3140,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434960</v>
+        <v>434938</v>
       </c>
       <c r="R25" t="n">
-        <v>6786370</v>
+        <v>6786813</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128430705</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434938</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786813</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,7 +3458,7 @@
         <v>128433812</v>
       </c>
       <c r="B28" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>128430536</v>
       </c>
       <c r="B29" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>128434019</v>
       </c>
       <c r="B36" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>128434393</v>
       </c>
       <c r="B37" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>128439013</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436784</v>
+        <v>128437738</v>
       </c>
       <c r="B39" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434955</v>
+        <v>434991</v>
       </c>
       <c r="R39" t="n">
-        <v>6786364</v>
+        <v>6786554</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437738</v>
+        <v>128438813</v>
       </c>
       <c r="B40" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434991</v>
+        <v>435222</v>
       </c>
       <c r="R40" t="n">
-        <v>6786554</v>
+        <v>6786653</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128438813</v>
+        <v>128436784</v>
       </c>
       <c r="B41" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435222</v>
+        <v>434955</v>
       </c>
       <c r="R41" t="n">
-        <v>6786653</v>
+        <v>6786364</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4956,7 +4956,7 @@
         <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B44" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5183,39 +5183,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R44" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5247,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5257,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5284,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128437639</v>
+        <v>128431219</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5295,34 +5290,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434969</v>
+        <v>434992</v>
       </c>
       <c r="R45" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5394,7 +5394,7 @@
         <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128433488</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>435012</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786629</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128436819</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>434960</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786373</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128436819</v>
+        <v>128431782</v>
       </c>
       <c r="B51" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434960</v>
+        <v>434911</v>
       </c>
       <c r="R51" t="n">
-        <v>6786373</v>
+        <v>6786765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128433488</v>
+        <v>128437246</v>
       </c>
       <c r="B52" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435012</v>
+        <v>434984</v>
       </c>
       <c r="R52" t="n">
-        <v>6786629</v>
+        <v>6786426</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128431782</v>
+        <v>128438534</v>
       </c>
       <c r="B53" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434911</v>
+        <v>435172</v>
       </c>
       <c r="R53" t="n">
-        <v>6786765</v>
+        <v>6786693</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128434045</v>
+        <v>128437455</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,21 +6258,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435021</v>
+        <v>434951</v>
       </c>
       <c r="R54" t="n">
-        <v>6786538</v>
+        <v>6786479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432659</v>
+        <v>128434045</v>
       </c>
       <c r="B55" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R55" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432698</v>
+        <v>128432659</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128433166</v>
+        <v>128432698</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6599,14 +6599,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R57" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,12 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432985</v>
+        <v>128433166</v>
       </c>
       <c r="B58" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,21 +6686,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6715,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435046</v>
+        <v>435052</v>
       </c>
       <c r="R58" t="n">
-        <v>6786693</v>
+        <v>6786677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6755,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128437455</v>
+        <v>128432985</v>
       </c>
       <c r="B59" t="n">
-        <v>78874</v>
+        <v>79739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434951</v>
+        <v>435046</v>
       </c>
       <c r="R59" t="n">
-        <v>6786479</v>
+        <v>6786693</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6897,7 +6897,7 @@
         <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128437830</v>
+        <v>128437303</v>
       </c>
       <c r="B61" t="n">
-        <v>78874</v>
+        <v>79739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434978</v>
+        <v>434966</v>
       </c>
       <c r="R61" t="n">
-        <v>6786579</v>
+        <v>6786443</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7111,7 +7111,7 @@
         <v>128432598</v>
       </c>
       <c r="B62" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128430267</v>
+        <v>128437830</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,34 +7226,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434893</v>
+        <v>434978</v>
       </c>
       <c r="R63" t="n">
-        <v>6786780</v>
+        <v>6786579</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128437303</v>
+        <v>128430267</v>
       </c>
       <c r="B64" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,34 +7333,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434966</v>
+        <v>434893</v>
       </c>
       <c r="R64" t="n">
-        <v>6786443</v>
+        <v>6786780</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
         <v>128433442</v>
       </c>
       <c r="B65" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128436694</v>
+        <v>128433951</v>
       </c>
       <c r="B67" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434968</v>
+        <v>435035</v>
       </c>
       <c r="R67" t="n">
-        <v>6786352</v>
+        <v>6786547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433951</v>
+        <v>128436694</v>
       </c>
       <c r="B68" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435035</v>
+        <v>434968</v>
       </c>
       <c r="R68" t="n">
-        <v>6786547</v>
+        <v>6786352</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7860,7 +7860,7 @@
         <v>128430389</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>128433768</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>128437208</v>
       </c>
       <c r="B71" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>128437404</v>
       </c>
       <c r="B75" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128438202</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>128434479</v>
       </c>
       <c r="B77" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B78" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R78" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,12 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,21 +8953,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8982,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9022,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128438473</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,39 +9065,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435172</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786698</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9129,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9139,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435643</v>
+        <v>128452309</v>
       </c>
       <c r="B81" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,34 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435049</v>
+        <v>434956</v>
       </c>
       <c r="R81" t="n">
-        <v>6786296</v>
+        <v>6786830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9268,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128452309</v>
+        <v>128438473</v>
       </c>
       <c r="B82" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9279,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434956</v>
+        <v>435172</v>
       </c>
       <c r="R82" t="n">
-        <v>6786830</v>
+        <v>6786698</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128432486</v>
+        <v>128430113</v>
       </c>
       <c r="B83" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434985</v>
+        <v>434877</v>
       </c>
       <c r="R83" t="n">
-        <v>6786751</v>
+        <v>6786784</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9455,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9465,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430337</v>
+        <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9522,10 +9527,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434911</v>
+        <v>434985</v>
       </c>
       <c r="R84" t="n">
-        <v>6786789</v>
+        <v>6786751</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9562,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9572,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,10 +9599,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128437508</v>
+        <v>128430337</v>
       </c>
       <c r="B85" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,34 +9610,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434949</v>
+        <v>434911</v>
       </c>
       <c r="R85" t="n">
-        <v>6786472</v>
+        <v>6786789</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9664,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9674,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9701,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128439136</v>
+        <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9712,21 +9717,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9736,10 +9741,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435263</v>
+        <v>434949</v>
       </c>
       <c r="R86" t="n">
-        <v>6786587</v>
+        <v>6786472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9771,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9781,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9808,10 +9813,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128430113</v>
+        <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9819,39 +9824,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434877</v>
+        <v>435263</v>
       </c>
       <c r="R87" t="n">
-        <v>6786784</v>
+        <v>6786587</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,45 +1174,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128432850</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>435037</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1249,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,7 +1286,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1312,7 +1317,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1321,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R8" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1371,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,50 +1398,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128438000</v>
+        <v>128435467</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434956</v>
+        <v>435067</v>
       </c>
       <c r="R9" t="n">
-        <v>6786742</v>
+        <v>6786325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128431234</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>434997</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437284</v>
+        <v>128437383</v>
       </c>
       <c r="B17" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,34 +2274,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434970</v>
+        <v>434967</v>
       </c>
       <c r="R17" t="n">
-        <v>6786443</v>
+        <v>6786456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2343,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,45 +2375,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437182</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434976</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786426</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2450,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437383</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,39 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434967</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2562,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,50 +2594,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128435997</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435005</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786307</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128436802</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434960</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786370</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128430705</v>
+        <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,34 +3140,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434938</v>
+        <v>434960</v>
       </c>
       <c r="R25" t="n">
-        <v>6786813</v>
+        <v>6786370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,50 +3343,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128435386</v>
+        <v>128433812</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435059</v>
+        <v>435031</v>
       </c>
       <c r="R27" t="n">
-        <v>6786346</v>
+        <v>6786549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,7 +3450,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128433812</v>
+        <v>128430536</v>
       </c>
       <c r="B28" t="n">
         <v>78878</v>
@@ -3486,14 +3481,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435031</v>
+        <v>434931</v>
       </c>
       <c r="R28" t="n">
-        <v>6786549</v>
+        <v>6786802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,45 +3557,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128430536</v>
+        <v>128435386</v>
       </c>
       <c r="B29" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434931</v>
+        <v>435059</v>
       </c>
       <c r="R29" t="n">
-        <v>6786802</v>
+        <v>6786346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128431051</v>
+        <v>128430028</v>
       </c>
       <c r="B30" t="n">
         <v>79120</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434967</v>
+        <v>434877</v>
       </c>
       <c r="R30" t="n">
-        <v>6786800</v>
+        <v>6786784</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128430028</v>
+        <v>128447259</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434877</v>
+        <v>435291</v>
       </c>
       <c r="R31" t="n">
-        <v>6786784</v>
+        <v>6786596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128447259</v>
+        <v>128431051</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435291</v>
+        <v>434967</v>
       </c>
       <c r="R32" t="n">
-        <v>6786596</v>
+        <v>6786800</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432994</v>
+        <v>128434019</v>
       </c>
       <c r="B34" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435043</v>
+        <v>435020</v>
       </c>
       <c r="R34" t="n">
-        <v>6786691</v>
+        <v>6786551</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434019</v>
+        <v>128432994</v>
       </c>
       <c r="B36" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435020</v>
+        <v>435043</v>
       </c>
       <c r="R36" t="n">
-        <v>6786551</v>
+        <v>6786691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128437738</v>
+        <v>128433384</v>
       </c>
       <c r="B39" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434991</v>
+        <v>435063</v>
       </c>
       <c r="R39" t="n">
-        <v>6786554</v>
+        <v>6786656</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,7 +4739,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438813</v>
+        <v>128436784</v>
       </c>
       <c r="B40" t="n">
         <v>79739</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435222</v>
+        <v>434955</v>
       </c>
       <c r="R40" t="n">
-        <v>6786653</v>
+        <v>6786364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128436784</v>
+        <v>128437738</v>
       </c>
       <c r="B41" t="n">
         <v>79739</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434955</v>
+        <v>434991</v>
       </c>
       <c r="R41" t="n">
-        <v>6786364</v>
+        <v>6786554</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128433384</v>
+        <v>128438813</v>
       </c>
       <c r="B42" t="n">
-        <v>79710</v>
+        <v>79739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435063</v>
+        <v>435222</v>
       </c>
       <c r="R42" t="n">
-        <v>6786656</v>
+        <v>6786653</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128431132</v>
+        <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434976</v>
+        <v>434969</v>
       </c>
       <c r="R43" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,7 +5130,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5145,7 +5140,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437639</v>
+        <v>128431219</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5183,34 +5178,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434969</v>
+        <v>434992</v>
       </c>
       <c r="R44" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431219</v>
+        <v>128431132</v>
       </c>
       <c r="B45" t="n">
         <v>57713</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434992</v>
+        <v>434976</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128433488</v>
+        <v>128438534</v>
       </c>
       <c r="B49" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435012</v>
+        <v>435172</v>
       </c>
       <c r="R49" t="n">
-        <v>6786629</v>
+        <v>6786693</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128431782</v>
+        <v>128433488</v>
       </c>
       <c r="B51" t="n">
         <v>78878</v>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434911</v>
+        <v>435012</v>
       </c>
       <c r="R51" t="n">
-        <v>6786765</v>
+        <v>6786629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128437246</v>
+        <v>128431782</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,34 +6044,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434984</v>
+        <v>434911</v>
       </c>
       <c r="R52" t="n">
-        <v>6786426</v>
+        <v>6786765</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,7 +6140,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B53" t="n">
         <v>79120</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R53" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,32 +6247,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128437455</v>
+        <v>128444055</v>
       </c>
       <c r="B54" t="n">
-        <v>78878</v>
+        <v>97503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434951</v>
+        <v>435327</v>
       </c>
       <c r="R54" t="n">
-        <v>6786479</v>
+        <v>6786584</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128434045</v>
+        <v>128432659</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435021</v>
+        <v>434995</v>
       </c>
       <c r="R55" t="n">
-        <v>6786538</v>
+        <v>6786753</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,7 +6461,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432659</v>
+        <v>128432985</v>
       </c>
       <c r="B56" t="n">
         <v>79739</v>
@@ -6492,14 +6492,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434995</v>
+        <v>435046</v>
       </c>
       <c r="R56" t="n">
-        <v>6786753</v>
+        <v>6786693</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,7 +6568,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432698</v>
+        <v>128434045</v>
       </c>
       <c r="B57" t="n">
         <v>79120</v>
@@ -6599,14 +6599,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R57" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,7 +6675,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128433166</v>
+        <v>128432698</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6706,14 +6706,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R58" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,12 +6755,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,10 +6782,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128432985</v>
+        <v>128433166</v>
       </c>
       <c r="B59" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6798,21 +6793,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435046</v>
+        <v>435052</v>
       </c>
       <c r="R59" t="n">
-        <v>6786693</v>
+        <v>6786677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6852,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6862,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128444055</v>
+        <v>128437455</v>
       </c>
       <c r="B60" t="n">
-        <v>97503</v>
+        <v>78878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435327</v>
+        <v>434951</v>
       </c>
       <c r="R60" t="n">
-        <v>6786584</v>
+        <v>6786479</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,32 +7001,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128437303</v>
+        <v>128434528</v>
       </c>
       <c r="B61" t="n">
-        <v>79739</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434966</v>
+        <v>435062</v>
       </c>
       <c r="R61" t="n">
-        <v>6786443</v>
+        <v>6786456</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128432598</v>
+        <v>128430267</v>
       </c>
       <c r="B62" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434985</v>
+        <v>434893</v>
       </c>
       <c r="R62" t="n">
-        <v>6786751</v>
+        <v>6786780</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7322,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128430267</v>
+        <v>128432598</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7333,21 +7333,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434893</v>
+        <v>434985</v>
       </c>
       <c r="R64" t="n">
-        <v>6786780</v>
+        <v>6786751</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128433442</v>
+        <v>128437303</v>
       </c>
       <c r="B65" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>435015</v>
+        <v>434966</v>
       </c>
       <c r="R65" t="n">
-        <v>6786627</v>
+        <v>6786443</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,32 +7536,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128434528</v>
+        <v>128433442</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78877</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435062</v>
+        <v>435015</v>
       </c>
       <c r="R66" t="n">
-        <v>6786456</v>
+        <v>6786627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128433951</v>
+        <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435035</v>
+        <v>435271</v>
       </c>
       <c r="R67" t="n">
-        <v>6786547</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7857,10 +7862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128430389</v>
+        <v>128433951</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,34 +7873,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434924</v>
+        <v>435035</v>
       </c>
       <c r="R69" t="n">
-        <v>6786800</v>
+        <v>6786547</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7964,7 +7969,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128433768</v>
+        <v>128430389</v>
       </c>
       <c r="B70" t="n">
         <v>79120</v>
@@ -7995,14 +8000,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435033</v>
+        <v>434924</v>
       </c>
       <c r="R70" t="n">
-        <v>6786548</v>
+        <v>6786800</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8044,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8071,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128437208</v>
+        <v>128433768</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434976</v>
+        <v>435033</v>
       </c>
       <c r="R71" t="n">
-        <v>6786430</v>
+        <v>6786548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8151,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8178,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128439118</v>
+        <v>128437208</v>
       </c>
       <c r="B72" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8189,39 +8194,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435271</v>
+        <v>434976</v>
       </c>
       <c r="R72" t="n">
-        <v>6786589</v>
+        <v>6786430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,7 +8290,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128437095</v>
+        <v>128434479</v>
       </c>
       <c r="B73" t="n">
         <v>79120</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434954</v>
+        <v>435046</v>
       </c>
       <c r="R73" t="n">
-        <v>6786401</v>
+        <v>6786473</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128433881</v>
+        <v>128437095</v>
       </c>
       <c r="B74" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8413,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435035</v>
+        <v>434954</v>
       </c>
       <c r="R74" t="n">
-        <v>6786547</v>
+        <v>6786401</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8472,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8482,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,10 +8509,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8520,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R75" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8579,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,7 +8589,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8611,7 +8616,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128438202</v>
+        <v>128437404</v>
       </c>
       <c r="B76" t="n">
         <v>79120</v>
@@ -8642,14 +8647,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435147</v>
+        <v>434956</v>
       </c>
       <c r="R76" t="n">
-        <v>6786737</v>
+        <v>6786459</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8681,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8691,12 +8696,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,7 +8723,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128434479</v>
+        <v>128438202</v>
       </c>
       <c r="B77" t="n">
         <v>79120</v>
@@ -8754,14 +8754,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435046</v>
+        <v>435147</v>
       </c>
       <c r="R77" t="n">
-        <v>6786473</v>
+        <v>6786737</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128435643</v>
+        <v>128438473</v>
       </c>
       <c r="B78" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,34 +8846,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435049</v>
+        <v>435172</v>
       </c>
       <c r="R78" t="n">
-        <v>6786296</v>
+        <v>6786698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8920,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,7 +8947,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128452309</v>
       </c>
       <c r="B79" t="n">
         <v>79120</v>
@@ -8973,14 +8978,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>434956</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786830</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,12 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B80" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9134,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128452309</v>
+        <v>128435513</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,34 +9177,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434956</v>
+        <v>435069</v>
       </c>
       <c r="R81" t="n">
-        <v>6786830</v>
+        <v>6786320</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9268,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128438473</v>
+        <v>128435643</v>
       </c>
       <c r="B82" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9279,39 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435172</v>
+        <v>435049</v>
       </c>
       <c r="R82" t="n">
-        <v>6786698</v>
+        <v>6786296</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B83" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,39 +9391,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R83" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9455,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9465,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9492,7 +9487,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128432486</v>
+        <v>128430337</v>
       </c>
       <c r="B84" t="n">
         <v>79120</v>
@@ -9527,10 +9522,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434985</v>
+        <v>434911</v>
       </c>
       <c r="R84" t="n">
-        <v>6786751</v>
+        <v>6786789</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9572,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,10 +9594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128430337</v>
+        <v>128430113</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9610,34 +9605,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434911</v>
+        <v>434877</v>
       </c>
       <c r="R85" t="n">
-        <v>6786789</v>
+        <v>6786784</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,7 +1174,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1205,7 +1205,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R7" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,50 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1356,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1371,7 +1366,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,45 +1393,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B9" t="n">
-        <v>79710</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R9" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R10" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -5712,7 +5712,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
         <v>79120</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128436819</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434960</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786373</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128433488</v>
+        <v>128436819</v>
       </c>
       <c r="B51" t="n">
         <v>78878</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435012</v>
+        <v>434960</v>
       </c>
       <c r="R51" t="n">
-        <v>6786629</v>
+        <v>6786373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,7 +6033,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128431782</v>
+        <v>128433488</v>
       </c>
       <c r="B52" t="n">
         <v>78878</v>
@@ -6064,14 +6064,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434911</v>
+        <v>435012</v>
       </c>
       <c r="R52" t="n">
-        <v>6786765</v>
+        <v>6786629</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128437246</v>
+        <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434984</v>
+        <v>434911</v>
       </c>
       <c r="R53" t="n">
-        <v>6786426</v>
+        <v>6786765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128439118</v>
+        <v>128430389</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,39 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435271</v>
+        <v>434924</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786800</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7718,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7728,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128436694</v>
+        <v>128433768</v>
       </c>
       <c r="B68" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,21 +7761,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7790,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434968</v>
+        <v>435033</v>
       </c>
       <c r="R68" t="n">
-        <v>6786352</v>
+        <v>6786548</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7835,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7862,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128433951</v>
+        <v>128437208</v>
       </c>
       <c r="B69" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,21 +7868,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7897,10 +7892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435035</v>
+        <v>434976</v>
       </c>
       <c r="R69" t="n">
-        <v>6786547</v>
+        <v>6786430</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128430389</v>
+        <v>128439118</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,34 +7975,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434924</v>
+        <v>435271</v>
       </c>
       <c r="R70" t="n">
-        <v>6786800</v>
+        <v>6786589</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128433768</v>
+        <v>128436694</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435033</v>
+        <v>434968</v>
       </c>
       <c r="R71" t="n">
-        <v>6786548</v>
+        <v>6786352</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128437208</v>
+        <v>128433951</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434976</v>
+        <v>435035</v>
       </c>
       <c r="R72" t="n">
-        <v>6786430</v>
+        <v>6786547</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128438473</v>
+        <v>128452309</v>
       </c>
       <c r="B78" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,39 +8846,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435172</v>
+        <v>434956</v>
       </c>
       <c r="R78" t="n">
-        <v>6786698</v>
+        <v>6786830</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8910,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8920,7 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,7 +8942,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128452309</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
         <v>79120</v>
@@ -8978,14 +8973,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434956</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786830</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9022,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,12 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435513</v>
+        <v>128438473</v>
       </c>
       <c r="B81" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,34 +9172,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435069</v>
+        <v>435172</v>
       </c>
       <c r="R81" t="n">
-        <v>6786320</v>
+        <v>6786698</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128432486</v>
+        <v>128437508</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434985</v>
+        <v>434949</v>
       </c>
       <c r="R83" t="n">
-        <v>6786751</v>
+        <v>6786472</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,7 +9487,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430337</v>
+        <v>128439136</v>
       </c>
       <c r="B84" t="n">
         <v>79120</v>
@@ -9518,14 +9518,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434911</v>
+        <v>435263</v>
       </c>
       <c r="R84" t="n">
-        <v>6786789</v>
+        <v>6786587</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9594,10 +9594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B85" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9605,39 +9605,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R85" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9664,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9674,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9706,10 +9701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128437508</v>
+        <v>128430337</v>
       </c>
       <c r="B86" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,34 +9712,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434949</v>
+        <v>434911</v>
       </c>
       <c r="R86" t="n">
-        <v>6786472</v>
+        <v>6786789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9776,7 +9771,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9786,7 +9781,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9813,10 +9808,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128439136</v>
+        <v>128430113</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9824,34 +9819,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435263</v>
+        <v>434877</v>
       </c>
       <c r="R87" t="n">
-        <v>6786587</v>
+        <v>6786784</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,50 +1174,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R7" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128431234</v>
+        <v>128438000</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434997</v>
+        <v>434956</v>
       </c>
       <c r="R8" t="n">
-        <v>6786800</v>
+        <v>6786742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128438143</v>
+        <v>128437383</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,34 +2060,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435139</v>
+        <v>434967</v>
       </c>
       <c r="R15" t="n">
-        <v>6786742</v>
+        <v>6786456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2124,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2134,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,45 +2161,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128431612</v>
+        <v>128435997</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434923</v>
+        <v>435005</v>
       </c>
       <c r="R16" t="n">
-        <v>6786779</v>
+        <v>6786307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2236,7 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437383</v>
+        <v>128437284</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,39 +2284,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434967</v>
+        <v>434970</v>
       </c>
       <c r="R17" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,50 +2380,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437182</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434976</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786426</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128431612</v>
       </c>
       <c r="B19" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>434923</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128438143</v>
       </c>
       <c r="B20" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>435139</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786742</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128437687</v>
+        <v>128433812</v>
       </c>
       <c r="B23" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434991</v>
+        <v>435031</v>
       </c>
       <c r="R23" t="n">
-        <v>6786553</v>
+        <v>6786549</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437480</v>
+        <v>128430536</v>
       </c>
       <c r="B24" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434949</v>
+        <v>434931</v>
       </c>
       <c r="R24" t="n">
-        <v>6786475</v>
+        <v>6786802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128436802</v>
+        <v>128437687</v>
       </c>
       <c r="B25" t="n">
         <v>78877</v>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434960</v>
+        <v>434991</v>
       </c>
       <c r="R25" t="n">
-        <v>6786370</v>
+        <v>6786553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128430705</v>
+        <v>128437480</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434938</v>
+        <v>434949</v>
       </c>
       <c r="R26" t="n">
-        <v>6786813</v>
+        <v>6786475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128433812</v>
+        <v>128436802</v>
       </c>
       <c r="B27" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435031</v>
+        <v>434960</v>
       </c>
       <c r="R27" t="n">
-        <v>6786549</v>
+        <v>6786370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430536</v>
+        <v>128430705</v>
       </c>
       <c r="B28" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434931</v>
+        <v>434938</v>
       </c>
       <c r="R28" t="n">
-        <v>6786802</v>
+        <v>6786813</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3669,7 +3669,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128430028</v>
+        <v>128431051</v>
       </c>
       <c r="B30" t="n">
         <v>79120</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434877</v>
+        <v>434967</v>
       </c>
       <c r="R30" t="n">
-        <v>6786784</v>
+        <v>6786800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128447259</v>
+        <v>128430028</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3807,14 +3807,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435291</v>
+        <v>434877</v>
       </c>
       <c r="R31" t="n">
-        <v>6786596</v>
+        <v>6786784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128431051</v>
+        <v>128447259</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -3914,14 +3914,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434967</v>
+        <v>435291</v>
       </c>
       <c r="R32" t="n">
-        <v>6786800</v>
+        <v>6786596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128434019</v>
+        <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435020</v>
+        <v>435043</v>
       </c>
       <c r="R34" t="n">
-        <v>6786551</v>
+        <v>6786691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128432204</v>
+        <v>128434019</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434949</v>
+        <v>435020</v>
       </c>
       <c r="R35" t="n">
-        <v>6786757</v>
+        <v>6786551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128432994</v>
+        <v>128434393</v>
       </c>
       <c r="B36" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435043</v>
+        <v>435046</v>
       </c>
       <c r="R36" t="n">
-        <v>6786691</v>
+        <v>6786471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434393</v>
+        <v>128439013</v>
       </c>
       <c r="B37" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435046</v>
+        <v>435264</v>
       </c>
       <c r="R37" t="n">
-        <v>6786471</v>
+        <v>6786618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,7 +4525,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128439013</v>
+        <v>128432204</v>
       </c>
       <c r="B38" t="n">
         <v>79120</v>
@@ -4556,14 +4556,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435264</v>
+        <v>434949</v>
       </c>
       <c r="R38" t="n">
-        <v>6786618</v>
+        <v>6786757</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128433384</v>
+        <v>128436784</v>
       </c>
       <c r="B39" t="n">
-        <v>79710</v>
+        <v>79739</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435063</v>
+        <v>434955</v>
       </c>
       <c r="R39" t="n">
-        <v>6786656</v>
+        <v>6786364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,7 +4739,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436784</v>
+        <v>128437738</v>
       </c>
       <c r="B40" t="n">
         <v>79739</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434955</v>
+        <v>434991</v>
       </c>
       <c r="R40" t="n">
-        <v>6786364</v>
+        <v>6786554</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437738</v>
+        <v>128438813</v>
       </c>
       <c r="B41" t="n">
         <v>79739</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434991</v>
+        <v>435222</v>
       </c>
       <c r="R41" t="n">
-        <v>6786554</v>
+        <v>6786653</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128438813</v>
+        <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435222</v>
+        <v>435063</v>
       </c>
       <c r="R42" t="n">
-        <v>6786653</v>
+        <v>6786656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437639</v>
+        <v>128431219</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434969</v>
+        <v>434992</v>
       </c>
       <c r="R43" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5135,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5140,7 +5145,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B44" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,39 +5183,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R44" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5712,7 +5712,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128438534</v>
       </c>
       <c r="B49" t="n">
         <v>79120</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>435172</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786693</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B50" t="n">
         <v>79120</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6247,45 +6247,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128444055</v>
+        <v>128432659</v>
       </c>
       <c r="B54" t="n">
-        <v>97503</v>
+        <v>79739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435327</v>
+        <v>434995</v>
       </c>
       <c r="R54" t="n">
-        <v>6786584</v>
+        <v>6786753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432659</v>
+        <v>128432698</v>
       </c>
       <c r="B55" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6568,32 +6568,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128434045</v>
+        <v>128444055</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>97503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435021</v>
+        <v>435327</v>
       </c>
       <c r="R57" t="n">
-        <v>6786538</v>
+        <v>6786584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432698</v>
+        <v>128437455</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6686,34 +6686,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R58" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128437455</v>
+        <v>128434045</v>
       </c>
       <c r="B60" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6905,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434951</v>
+        <v>435021</v>
       </c>
       <c r="R60" t="n">
-        <v>6786479</v>
+        <v>6786538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,45 +7001,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128434528</v>
+        <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435062</v>
+        <v>434893</v>
       </c>
       <c r="R61" t="n">
-        <v>6786456</v>
+        <v>6786780</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128430267</v>
+        <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434893</v>
+        <v>434966</v>
       </c>
       <c r="R62" t="n">
-        <v>6786780</v>
+        <v>6786443</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128437830</v>
+        <v>128433442</v>
       </c>
       <c r="B63" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434978</v>
+        <v>435015</v>
       </c>
       <c r="R63" t="n">
-        <v>6786579</v>
+        <v>6786627</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,45 +7322,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128432598</v>
+        <v>128434528</v>
       </c>
       <c r="B64" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434985</v>
+        <v>435062</v>
       </c>
       <c r="R64" t="n">
-        <v>6786751</v>
+        <v>6786456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437303</v>
+        <v>128437830</v>
       </c>
       <c r="B65" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434966</v>
+        <v>434978</v>
       </c>
       <c r="R65" t="n">
-        <v>6786443</v>
+        <v>6786579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,10 +7536,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128433442</v>
+        <v>128432598</v>
       </c>
       <c r="B66" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7547,34 +7547,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435015</v>
+        <v>434985</v>
       </c>
       <c r="R66" t="n">
-        <v>6786627</v>
+        <v>6786751</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128433768</v>
+        <v>128437208</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,21 +7761,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>435033</v>
+        <v>434976</v>
       </c>
       <c r="R68" t="n">
-        <v>6786548</v>
+        <v>6786430</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128437208</v>
+        <v>128433768</v>
       </c>
       <c r="B69" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7868,21 +7868,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434976</v>
+        <v>435033</v>
       </c>
       <c r="R69" t="n">
-        <v>6786430</v>
+        <v>6786548</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8290,7 +8290,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128434479</v>
+        <v>128437404</v>
       </c>
       <c r="B73" t="n">
         <v>79120</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435046</v>
+        <v>434956</v>
       </c>
       <c r="R73" t="n">
-        <v>6786473</v>
+        <v>6786459</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,12 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8402,7 +8397,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128437095</v>
+        <v>128434479</v>
       </c>
       <c r="B74" t="n">
         <v>79120</v>
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434954</v>
+        <v>435046</v>
       </c>
       <c r="R74" t="n">
-        <v>6786401</v>
+        <v>6786473</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8482,7 +8477,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128433881</v>
+        <v>128437095</v>
       </c>
       <c r="B75" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8520,21 +8520,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435035</v>
+        <v>434954</v>
       </c>
       <c r="R75" t="n">
-        <v>6786547</v>
+        <v>6786401</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8616,10 +8616,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8627,21 +8627,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R76" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,12 +9022,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9049,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128438473</v>
       </c>
       <c r="B80" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,34 +9060,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435172</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B81" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,39 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R81" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128437508</v>
+        <v>128430337</v>
       </c>
       <c r="B83" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434949</v>
+        <v>434911</v>
       </c>
       <c r="R83" t="n">
-        <v>6786472</v>
+        <v>6786789</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128439136</v>
+        <v>128430113</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9498,34 +9498,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435263</v>
+        <v>434877</v>
       </c>
       <c r="R84" t="n">
-        <v>6786587</v>
+        <v>6786784</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,7 +9562,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9567,7 +9572,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9701,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128430337</v>
+        <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9712,34 +9717,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434911</v>
+        <v>434949</v>
       </c>
       <c r="R86" t="n">
-        <v>6786789</v>
+        <v>6786472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9771,7 +9776,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9781,7 +9786,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9808,10 +9813,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128430113</v>
+        <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9819,39 +9824,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434877</v>
+        <v>435263</v>
       </c>
       <c r="R87" t="n">
-        <v>6786784</v>
+        <v>6786587</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>128432333</v>
       </c>
       <c r="B90" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>128526361</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>128440167</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1177,7 +1177,7 @@
         <v>128431234</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128435467</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>128435686</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>128437383</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,50 +2161,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128435997</v>
+        <v>128438143</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435005</v>
+        <v>435139</v>
       </c>
       <c r="R16" t="n">
-        <v>6786307</v>
+        <v>6786742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437284</v>
+        <v>128431612</v>
       </c>
       <c r="B17" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,34 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434970</v>
+        <v>434923</v>
       </c>
       <c r="R17" t="n">
-        <v>6786443</v>
+        <v>6786779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,45 +2375,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437182</v>
+        <v>128435997</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434976</v>
+        <v>435005</v>
       </c>
       <c r="R18" t="n">
-        <v>6786426</v>
+        <v>6786307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128431612</v>
+        <v>128437284</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434923</v>
+        <v>434970</v>
       </c>
       <c r="R19" t="n">
-        <v>6786779</v>
+        <v>6786443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128438143</v>
+        <v>128437182</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435139</v>
+        <v>434976</v>
       </c>
       <c r="R20" t="n">
-        <v>6786742</v>
+        <v>6786426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128433812</v>
+        <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>78881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435031</v>
+        <v>434991</v>
       </c>
       <c r="R23" t="n">
-        <v>6786549</v>
+        <v>6786553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128430536</v>
+        <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434931</v>
+        <v>434949</v>
       </c>
       <c r="R24" t="n">
-        <v>6786802</v>
+        <v>6786475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437687</v>
+        <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434991</v>
+        <v>434960</v>
       </c>
       <c r="R25" t="n">
-        <v>6786553</v>
+        <v>6786370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437480</v>
+        <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,34 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434949</v>
+        <v>434938</v>
       </c>
       <c r="R26" t="n">
-        <v>6786475</v>
+        <v>6786813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128436802</v>
+        <v>128433812</v>
       </c>
       <c r="B27" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434960</v>
+        <v>435031</v>
       </c>
       <c r="R27" t="n">
-        <v>6786370</v>
+        <v>6786549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128430705</v>
+        <v>128430536</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434938</v>
+        <v>434931</v>
       </c>
       <c r="R28" t="n">
-        <v>6786813</v>
+        <v>6786802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,7 +3672,7 @@
         <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434019</v>
+        <v>128432204</v>
       </c>
       <c r="B35" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435020</v>
+        <v>434949</v>
       </c>
       <c r="R35" t="n">
-        <v>6786551</v>
+        <v>6786757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434393</v>
+        <v>128434019</v>
       </c>
       <c r="B36" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435046</v>
+        <v>435020</v>
       </c>
       <c r="R36" t="n">
-        <v>6786471</v>
+        <v>6786551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128439013</v>
+        <v>128434393</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435264</v>
+        <v>435046</v>
       </c>
       <c r="R37" t="n">
-        <v>6786618</v>
+        <v>6786471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128432204</v>
+        <v>128439013</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,14 +4556,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434949</v>
+        <v>435264</v>
       </c>
       <c r="R38" t="n">
-        <v>6786757</v>
+        <v>6786618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,7 +4635,7 @@
         <v>128436784</v>
       </c>
       <c r="B39" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>128437738</v>
       </c>
       <c r="B40" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>128438813</v>
       </c>
       <c r="B41" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>128433384</v>
       </c>
       <c r="B42" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128431219</v>
+        <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434992</v>
+        <v>434969</v>
       </c>
       <c r="R43" t="n">
-        <v>6786804</v>
+        <v>6786551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,7 +5130,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5145,7 +5140,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437639</v>
+        <v>128431132</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5183,34 +5178,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434969</v>
+        <v>434976</v>
       </c>
       <c r="R44" t="n">
-        <v>6786551</v>
+        <v>6786804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431132</v>
+        <v>128431219</v>
       </c>
       <c r="B45" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434976</v>
+        <v>434992</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5394,7 +5394,7 @@
         <v>128429395</v>
       </c>
       <c r="B46" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128438534</v>
+        <v>128437246</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435172</v>
+        <v>434984</v>
       </c>
       <c r="R49" t="n">
-        <v>6786693</v>
+        <v>6786426</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128437246</v>
+        <v>128438534</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434984</v>
+        <v>435172</v>
       </c>
       <c r="R50" t="n">
-        <v>6786426</v>
+        <v>6786693</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,7 +5929,7 @@
         <v>128436819</v>
       </c>
       <c r="B51" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>128433488</v>
       </c>
       <c r="B52" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>128431782</v>
       </c>
       <c r="B53" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128432659</v>
+        <v>128434045</v>
       </c>
       <c r="B54" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,34 +6258,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R54" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432698</v>
+        <v>128432659</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432985</v>
+        <v>128432698</v>
       </c>
       <c r="B56" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,34 +6472,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435046</v>
+        <v>434995</v>
       </c>
       <c r="R56" t="n">
-        <v>6786693</v>
+        <v>6786753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,32 +6568,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128444055</v>
+        <v>128433166</v>
       </c>
       <c r="B57" t="n">
-        <v>97503</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435327</v>
+        <v>435052</v>
       </c>
       <c r="R57" t="n">
-        <v>6786584</v>
+        <v>6786677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,10 +6680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128437455</v>
+        <v>128432985</v>
       </c>
       <c r="B58" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6686,21 +6691,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6710,10 +6715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434951</v>
+        <v>435046</v>
       </c>
       <c r="R58" t="n">
-        <v>6786479</v>
+        <v>6786693</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6782,32 +6787,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128433166</v>
+        <v>128444055</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>97507</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435052</v>
+        <v>435327</v>
       </c>
       <c r="R59" t="n">
-        <v>6786677</v>
+        <v>6786584</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6852,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6862,12 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128434045</v>
+        <v>128437455</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6905,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435021</v>
+        <v>434951</v>
       </c>
       <c r="R60" t="n">
-        <v>6786538</v>
+        <v>6786479</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7004,7 +7004,7 @@
         <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>128437303</v>
       </c>
       <c r="B62" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>128433442</v>
       </c>
       <c r="B63" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>128437830</v>
       </c>
       <c r="B65" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>128432598</v>
       </c>
       <c r="B66" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128430389</v>
+        <v>128439118</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,34 +7654,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434924</v>
+        <v>435271</v>
       </c>
       <c r="R67" t="n">
-        <v>6786800</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7713,7 +7718,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7723,7 +7728,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7755,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128437208</v>
+        <v>128430389</v>
       </c>
       <c r="B68" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,34 +7766,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434976</v>
+        <v>434924</v>
       </c>
       <c r="R68" t="n">
-        <v>6786430</v>
+        <v>6786800</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7830,7 +7835,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7860,7 +7865,7 @@
         <v>128433768</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7964,10 +7969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128439118</v>
+        <v>128437208</v>
       </c>
       <c r="B70" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,39 +7980,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435271</v>
+        <v>434976</v>
       </c>
       <c r="R70" t="n">
-        <v>6786589</v>
+        <v>6786430</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8079,7 +8079,7 @@
         <v>128436694</v>
       </c>
       <c r="B71" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>128433951</v>
       </c>
       <c r="B72" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128437404</v>
+        <v>128437095</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434956</v>
+        <v>434954</v>
       </c>
       <c r="R73" t="n">
-        <v>6786459</v>
+        <v>6786401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128434479</v>
+        <v>128433881</v>
       </c>
       <c r="B74" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435046</v>
+        <v>435035</v>
       </c>
       <c r="R74" t="n">
-        <v>6786473</v>
+        <v>6786547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,12 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på en radie av 30 m.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8509,10 +8504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437095</v>
+        <v>128437404</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434954</v>
+        <v>434956</v>
       </c>
       <c r="R75" t="n">
-        <v>6786401</v>
+        <v>6786459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8579,7 +8574,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8589,7 +8584,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8616,10 +8611,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128433881</v>
+        <v>128438202</v>
       </c>
       <c r="B76" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8627,34 +8622,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>435035</v>
+        <v>435147</v>
       </c>
       <c r="R76" t="n">
-        <v>6786547</v>
+        <v>6786737</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8686,7 +8681,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8696,7 +8691,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128438202</v>
+        <v>128434479</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8754,14 +8754,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>435147</v>
+        <v>435046</v>
       </c>
       <c r="R77" t="n">
-        <v>6786737</v>
+        <v>6786473</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Granskog som är rikligt draperad med garnlav, radie på 50 m</t>
+          <t>Rikligt med garnlav på en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128452309</v>
+        <v>128438473</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,34 +8846,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434956</v>
+        <v>435172</v>
       </c>
       <c r="R78" t="n">
-        <v>6786830</v>
+        <v>6786698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,7 +8920,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8942,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435513</v>
+        <v>128434156</v>
       </c>
       <c r="B79" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8953,21 +8958,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8977,10 +8982,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435069</v>
+        <v>435002</v>
       </c>
       <c r="R79" t="n">
-        <v>6786320</v>
+        <v>6786518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9012,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9022,7 +9027,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9049,10 +9059,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128438473</v>
+        <v>128435513</v>
       </c>
       <c r="B80" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9060,39 +9070,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435172</v>
+        <v>435069</v>
       </c>
       <c r="R80" t="n">
-        <v>6786698</v>
+        <v>6786320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9139,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9166,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9172,21 +9177,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R81" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9236,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,12 +9246,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128435643</v>
+        <v>128452309</v>
       </c>
       <c r="B82" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435049</v>
+        <v>434956</v>
       </c>
       <c r="R82" t="n">
-        <v>6786296</v>
+        <v>6786830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128430337</v>
+        <v>128430113</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9391,34 +9391,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434911</v>
+        <v>434877</v>
       </c>
       <c r="R83" t="n">
-        <v>6786789</v>
+        <v>6786784</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9450,7 +9455,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9460,7 +9465,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128430113</v>
+        <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9498,39 +9503,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434877</v>
+        <v>434985</v>
       </c>
       <c r="R84" t="n">
-        <v>6786784</v>
+        <v>6786751</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9599,10 +9599,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128432486</v>
+        <v>128430337</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434985</v>
+        <v>434911</v>
       </c>
       <c r="R85" t="n">
-        <v>6786751</v>
+        <v>6786789</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9709,7 +9709,7 @@
         <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432994</v>
+        <v>128432204</v>
       </c>
       <c r="B34" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435043</v>
+        <v>434949</v>
       </c>
       <c r="R34" t="n">
-        <v>6786691</v>
+        <v>6786757</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128432204</v>
+        <v>128434019</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434949</v>
+        <v>435020</v>
       </c>
       <c r="R35" t="n">
-        <v>6786757</v>
+        <v>6786551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,7 +4311,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434019</v>
+        <v>128434393</v>
       </c>
       <c r="B36" t="n">
         <v>78881</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435020</v>
+        <v>435046</v>
       </c>
       <c r="R36" t="n">
-        <v>6786551</v>
+        <v>6786471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128434393</v>
+        <v>128439013</v>
       </c>
       <c r="B37" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435046</v>
+        <v>435264</v>
       </c>
       <c r="R37" t="n">
-        <v>6786471</v>
+        <v>6786618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128439013</v>
+        <v>128432994</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435264</v>
+        <v>435043</v>
       </c>
       <c r="R38" t="n">
-        <v>6786618</v>
+        <v>6786691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6247,32 +6247,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128434045</v>
+        <v>128444055</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>97507</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435021</v>
+        <v>435327</v>
       </c>
       <c r="R54" t="n">
-        <v>6786538</v>
+        <v>6786584</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128432659</v>
+        <v>128437455</v>
       </c>
       <c r="B55" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434995</v>
+        <v>434951</v>
       </c>
       <c r="R55" t="n">
-        <v>6786753</v>
+        <v>6786479</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,7 +6461,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128432698</v>
+        <v>128434045</v>
       </c>
       <c r="B56" t="n">
         <v>79124</v>
@@ -6492,14 +6492,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434995</v>
+        <v>435021</v>
       </c>
       <c r="R56" t="n">
-        <v>6786753</v>
+        <v>6786538</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128433166</v>
+        <v>128432659</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,34 +6579,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435052</v>
+        <v>434995</v>
       </c>
       <c r="R57" t="n">
-        <v>6786677</v>
+        <v>6786753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,12 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432985</v>
+        <v>128432698</v>
       </c>
       <c r="B58" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6691,34 +6686,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435046</v>
+        <v>434995</v>
       </c>
       <c r="R58" t="n">
-        <v>6786693</v>
+        <v>6786753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6760,7 +6755,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6787,32 +6782,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128444055</v>
+        <v>128433166</v>
       </c>
       <c r="B59" t="n">
-        <v>97507</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435327</v>
+        <v>435052</v>
       </c>
       <c r="R59" t="n">
-        <v>6786584</v>
+        <v>6786677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6852,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6867,7 +6862,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128437455</v>
+        <v>128432985</v>
       </c>
       <c r="B60" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6905,21 +6905,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434951</v>
+        <v>435046</v>
       </c>
       <c r="R60" t="n">
-        <v>6786479</v>
+        <v>6786693</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128438473</v>
+        <v>128434156</v>
       </c>
       <c r="B78" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,39 +8846,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435172</v>
+        <v>435002</v>
       </c>
       <c r="R78" t="n">
-        <v>6786698</v>
+        <v>6786518</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8910,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8920,7 +8915,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8947,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128434156</v>
+        <v>128435513</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,21 +8958,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435002</v>
+        <v>435069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786518</v>
+        <v>6786320</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,12 +9027,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435513</v>
+        <v>128435643</v>
       </c>
       <c r="B80" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9070,21 +9065,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435069</v>
+        <v>435049</v>
       </c>
       <c r="R80" t="n">
-        <v>6786320</v>
+        <v>6786296</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9129,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9139,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128435643</v>
+        <v>128452309</v>
       </c>
       <c r="B81" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9177,34 +9172,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435049</v>
+        <v>434956</v>
       </c>
       <c r="R81" t="n">
-        <v>6786296</v>
+        <v>6786830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9236,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9246,7 +9241,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9273,10 +9268,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128452309</v>
+        <v>128438473</v>
       </c>
       <c r="B82" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9284,34 +9279,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434956</v>
+        <v>435172</v>
       </c>
       <c r="R82" t="n">
-        <v>6786830</v>
+        <v>6786698</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 36327-2025 artfynd.xlsx
+++ b/artfynd/A 36327-2025 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128431234</v>
+        <v>128435467</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434997</v>
+        <v>435067</v>
       </c>
       <c r="R7" t="n">
-        <v>6786800</v>
+        <v>6786325</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128438000</v>
+        <v>128431234</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434956</v>
+        <v>434997</v>
       </c>
       <c r="R8" t="n">
-        <v>6786742</v>
+        <v>6786800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1351,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,7 +1361,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128432850</v>
+        <v>128438000</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1424,7 +1419,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435037</v>
+        <v>434956</v>
       </c>
       <c r="R9" t="n">
-        <v>6786731</v>
+        <v>6786742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1463,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1473,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,45 +1500,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128435467</v>
+        <v>128432850</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435067</v>
+        <v>435037</v>
       </c>
       <c r="R10" t="n">
-        <v>6786325</v>
+        <v>6786731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1615,7 @@
         <v>128435686</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128430866</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128437673</v>
       </c>
       <c r="B13" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128432871</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437383</v>
+        <v>128437284</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,39 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434967</v>
+        <v>434970</v>
       </c>
       <c r="R15" t="n">
-        <v>6786456</v>
+        <v>6786443</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128438143</v>
+        <v>128437182</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2167,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435139</v>
+        <v>434976</v>
       </c>
       <c r="R16" t="n">
-        <v>6786742</v>
+        <v>6786426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,45 +2263,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128431612</v>
+        <v>128435997</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434923</v>
+        <v>435005</v>
       </c>
       <c r="R17" t="n">
-        <v>6786779</v>
+        <v>6786307</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,38 +2375,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128435997</v>
+        <v>128437383</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435005</v>
+        <v>434967</v>
       </c>
       <c r="R18" t="n">
-        <v>6786307</v>
+        <v>6786456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128437284</v>
+        <v>128438143</v>
       </c>
       <c r="B19" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,34 +2498,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434970</v>
+        <v>435139</v>
       </c>
       <c r="R19" t="n">
-        <v>6786443</v>
+        <v>6786742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128437182</v>
+        <v>128431612</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434976</v>
+        <v>434923</v>
       </c>
       <c r="R20" t="n">
-        <v>6786426</v>
+        <v>6786779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2704,7 @@
         <v>128451721</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128434385</v>
       </c>
       <c r="B22" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128437687</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128437480</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>128436802</v>
       </c>
       <c r="B25" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>128430705</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>128433812</v>
       </c>
       <c r="B27" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128430536</v>
       </c>
       <c r="B28" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>128431051</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>128430028</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128447259</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>128431641</v>
       </c>
       <c r="B33" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128432204</v>
+        <v>128432994</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434949</v>
+        <v>435043</v>
       </c>
       <c r="R34" t="n">
-        <v>6786757</v>
+        <v>6786691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128434019</v>
+        <v>128439013</v>
       </c>
       <c r="B35" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435020</v>
+        <v>435264</v>
       </c>
       <c r="R35" t="n">
-        <v>6786551</v>
+        <v>6786618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128434393</v>
+        <v>128432204</v>
       </c>
       <c r="B36" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,34 +4322,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435046</v>
+        <v>434949</v>
       </c>
       <c r="R36" t="n">
-        <v>6786471</v>
+        <v>6786757</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128439013</v>
+        <v>128434019</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435264</v>
+        <v>435020</v>
       </c>
       <c r="R37" t="n">
-        <v>6786618</v>
+        <v>6786551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128432994</v>
+        <v>128434393</v>
       </c>
       <c r="B38" t="n">
-        <v>78882</v>
+        <v>78786</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435043</v>
+        <v>435046</v>
       </c>
       <c r="R38" t="n">
-        <v>6786691</v>
+        <v>6786471</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4632,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436784</v>
+        <v>128433384</v>
       </c>
       <c r="B39" t="n">
-        <v>79743</v>
+        <v>79619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434955</v>
+        <v>435063</v>
       </c>
       <c r="R39" t="n">
-        <v>6786364</v>
+        <v>6786656</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437738</v>
+        <v>128436784</v>
       </c>
       <c r="B40" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434991</v>
+        <v>434955</v>
       </c>
       <c r="R40" t="n">
-        <v>6786554</v>
+        <v>6786364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128438813</v>
+        <v>128437738</v>
       </c>
       <c r="B41" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435222</v>
+        <v>434991</v>
       </c>
       <c r="R41" t="n">
-        <v>6786653</v>
+        <v>6786554</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128433384</v>
+        <v>128438813</v>
       </c>
       <c r="B42" t="n">
-        <v>79714</v>
+        <v>79648</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,21 +4964,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435063</v>
+        <v>435222</v>
       </c>
       <c r="R42" t="n">
-        <v>6786656</v>
+        <v>6786653</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5063,7 +5063,7 @@
         <v>128437639</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128431132</v>
+        <v>128429395</v>
       </c>
       <c r="B44" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,39 +5178,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434976</v>
+        <v>434860</v>
       </c>
       <c r="R44" t="n">
-        <v>6786804</v>
+        <v>6786796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5242,7 +5237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5252,7 +5247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128431219</v>
+        <v>128431132</v>
       </c>
       <c r="B45" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434992</v>
+        <v>434976</v>
       </c>
       <c r="R45" t="n">
         <v>6786804</v>
@@ -5354,7 +5349,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5364,7 +5359,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5391,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128429395</v>
+        <v>128431219</v>
       </c>
       <c r="B46" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5402,34 +5397,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434860</v>
+        <v>434992</v>
       </c>
       <c r="R46" t="n">
-        <v>6786796</v>
+        <v>6786804</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5501,7 +5501,7 @@
         <v>128433187</v>
       </c>
       <c r="B47" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>128437823</v>
       </c>
       <c r="B48" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128437246</v>
+        <v>128436819</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,21 +5723,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434984</v>
+        <v>434960</v>
       </c>
       <c r="R49" t="n">
-        <v>6786426</v>
+        <v>6786373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128438534</v>
+        <v>128433488</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5830,21 +5830,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435172</v>
+        <v>435012</v>
       </c>
       <c r="R50" t="n">
-        <v>6786693</v>
+        <v>6786629</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128436819</v>
+        <v>128431782</v>
       </c>
       <c r="B51" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5957,14 +5957,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434960</v>
+        <v>434911</v>
       </c>
       <c r="R51" t="n">
-        <v>6786373</v>
+        <v>6786765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128433488</v>
+        <v>128437246</v>
       </c>
       <c r="B52" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435012</v>
+        <v>434984</v>
       </c>
       <c r="R52" t="n">
-        <v>6786629</v>
+        <v>6786426</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128431782</v>
+        <v>128438534</v>
       </c>
       <c r="B53" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434911</v>
+        <v>435172</v>
       </c>
       <c r="R53" t="n">
-        <v>6786765</v>
+        <v>6786693</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6247,32 +6247,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128444055</v>
+        <v>128437455</v>
       </c>
       <c r="B54" t="n">
-        <v>97507</v>
+        <v>78787</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435327</v>
+        <v>434951</v>
       </c>
       <c r="R54" t="n">
-        <v>6786584</v>
+        <v>6786479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128437455</v>
+        <v>128434045</v>
       </c>
       <c r="B55" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434951</v>
+        <v>435021</v>
       </c>
       <c r="R55" t="n">
-        <v>6786479</v>
+        <v>6786538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128434045</v>
+        <v>128432659</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,34 +6472,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435021</v>
+        <v>434995</v>
       </c>
       <c r="R56" t="n">
-        <v>6786538</v>
+        <v>6786753</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6568,10 +6568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128432659</v>
+        <v>128432698</v>
       </c>
       <c r="B57" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,21 +6579,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128432698</v>
+        <v>128433166</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6706,14 +6706,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434995</v>
+        <v>435052</v>
       </c>
       <c r="R58" t="n">
-        <v>6786753</v>
+        <v>6786677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6755,7 +6755,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6782,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128433166</v>
+        <v>128432985</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6793,21 +6798,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435052</v>
+        <v>435046</v>
       </c>
       <c r="R59" t="n">
-        <v>6786677</v>
+        <v>6786693</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6852,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6862,12 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på flera av tallarna inom en radie av 20-30 m.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6894,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128432985</v>
+        <v>128444055</v>
       </c>
       <c r="B60" t="n">
-        <v>79743</v>
+        <v>97514</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435046</v>
+        <v>435327</v>
       </c>
       <c r="R60" t="n">
-        <v>6786693</v>
+        <v>6786584</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7004,7 +7004,7 @@
         <v>128430267</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128437303</v>
+        <v>128433442</v>
       </c>
       <c r="B62" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434966</v>
+        <v>435015</v>
       </c>
       <c r="R62" t="n">
-        <v>6786443</v>
+        <v>6786627</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7215,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128433442</v>
+        <v>128437303</v>
       </c>
       <c r="B63" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7226,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435015</v>
+        <v>434966</v>
       </c>
       <c r="R63" t="n">
-        <v>6786627</v>
+        <v>6786443</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,32 +7322,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128434528</v>
+        <v>128437830</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78787</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435062</v>
+        <v>434978</v>
       </c>
       <c r="R64" t="n">
-        <v>6786456</v>
+        <v>6786579</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128437830</v>
+        <v>128432598</v>
       </c>
       <c r="B65" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7460,14 +7460,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434978</v>
+        <v>434985</v>
       </c>
       <c r="R65" t="n">
-        <v>6786579</v>
+        <v>6786751</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7536,45 +7536,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128432598</v>
+        <v>128434528</v>
       </c>
       <c r="B66" t="n">
-        <v>78882</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434985</v>
+        <v>435062</v>
       </c>
       <c r="R66" t="n">
-        <v>6786751</v>
+        <v>6786456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128439118</v>
+        <v>128436694</v>
       </c>
       <c r="B67" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7654,39 +7654,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435271</v>
+        <v>434968</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786352</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7718,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7728,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128430389</v>
+        <v>128433951</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,34 +7761,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434924</v>
+        <v>435035</v>
       </c>
       <c r="R68" t="n">
-        <v>6786800</v>
+        <v>6786547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7835,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7862,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128433768</v>
+        <v>128439118</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,34 +7868,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435033</v>
+        <v>435271</v>
       </c>
       <c r="R69" t="n">
-        <v>6786548</v>
+        <v>6786589</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128437208</v>
+        <v>128430389</v>
       </c>
       <c r="B70" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,34 +7980,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434976</v>
+        <v>434924</v>
       </c>
       <c r="R70" t="n">
-        <v>6786430</v>
+        <v>6786800</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128436694</v>
+        <v>128433768</v>
       </c>
       <c r="B71" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434968</v>
+        <v>435033</v>
       </c>
       <c r="R71" t="n">
-        <v>6786352</v>
+        <v>6786548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128433951</v>
+        <v>128437208</v>
       </c>
       <c r="B72" t="n">
-        <v>78882</v>
+        <v>78786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435035</v>
+        <v>434976</v>
       </c>
       <c r="R72" t="n">
-        <v>6786547</v>
+        <v>6786430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128437095</v>
+        <v>128437404</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434954</v>
+        <v>434956</v>
       </c>
       <c r="R73" t="n">
-        <v>6786401</v>
+        <v>6786459</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128433881</v>
+        <v>128437095</v>
       </c>
       <c r="B74" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435035</v>
+        <v>434954</v>
       </c>
       <c r="R74" t="n">
-        <v>6786547</v>
+        <v>6786401</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8504,10 +8504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128437404</v>
+        <v>128433881</v>
       </c>
       <c r="B75" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434956</v>
+        <v>435035</v>
       </c>
       <c r="R75" t="n">
-        <v>6786459</v>
+        <v>6786547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8614,7 +8614,7 @@
         <v>128438202</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>128434479</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128434156</v>
+        <v>128435643</v>
       </c>
       <c r="B78" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435002</v>
+        <v>435049</v>
       </c>
       <c r="R78" t="n">
-        <v>6786518</v>
+        <v>6786296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8915,12 +8915,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8947,10 +8942,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128435513</v>
+        <v>128452309</v>
       </c>
       <c r="B79" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8958,34 +8953,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalhusberg, Skalhusberg, Dlr</t>
+          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435069</v>
+        <v>434956</v>
       </c>
       <c r="R79" t="n">
-        <v>6786320</v>
+        <v>6786830</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9017,7 +9012,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9027,7 +9022,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9054,10 +9049,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128435643</v>
+        <v>128438473</v>
       </c>
       <c r="B80" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9065,34 +9060,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435049</v>
+        <v>435172</v>
       </c>
       <c r="R80" t="n">
-        <v>6786296</v>
+        <v>6786698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9161,10 +9161,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128452309</v>
+        <v>128434156</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9192,14 +9192,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skalhustjärnen, Skalhustjärnen, Dlr</t>
+          <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434956</v>
+        <v>435002</v>
       </c>
       <c r="R81" t="n">
-        <v>6786830</v>
+        <v>6786518</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9241,7 +9241,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på granar och tallar inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9268,10 +9273,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128438473</v>
+        <v>128435513</v>
       </c>
       <c r="B82" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9279,39 +9284,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalhusberg, Skalhusberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435172</v>
+        <v>435069</v>
       </c>
       <c r="R82" t="n">
-        <v>6786698</v>
+        <v>6786320</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9383,7 +9383,7 @@
         <v>128430113</v>
       </c>
       <c r="B83" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>128432486</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>128430337</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>128437508</v>
       </c>
       <c r="B86" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>128439136</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>128430991</v>
       </c>
       <c r="B88" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>128433568</v>
       </c>
       <c r="B89" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>128432333</v>
       </c>
       <c r="B90" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>128526361</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>128440167</v>
       </c>
       <c r="B92" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
